--- a/TUFE_Konfigurasyon.xlsx
+++ b/TUFE_Konfigurasyon.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\vb41981\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\vb40890\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D8E8EB2-97B6-452A-A402-FEBB2DEF78ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F8215E0-1858-4644-9DBB-958C6A4D49AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Madde_Sepeti" sheetId="1" r:id="rId1"/>
@@ -3564,16 +3564,15 @@
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="51.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="16.28515625" customWidth="1"/>
-    <col min="5" max="5" width="27.140625" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" customWidth="1"/>
-    <col min="7" max="7" width="15.5703125" customWidth="1"/>
-    <col min="8" max="8" width="54" customWidth="1"/>
-    <col min="9" max="9" width="111.140625" customWidth="1"/>
-    <col min="10" max="10" width="11.140625" customWidth="1"/>
-    <col min="11" max="11" width="41" customWidth="1"/>
-    <col min="12" max="12" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="115.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="111.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="184.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="255.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="13.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8668,7 +8667,7 @@
       <c r="J198" s="6"/>
       <c r="K198" s="6"/>
       <c r="M198">
-        <v>52</v>
+        <v>54.87</v>
       </c>
     </row>
     <row r="199" spans="1:13" x14ac:dyDescent="0.25">
@@ -8728,7 +8727,7 @@
       <c r="J200" s="6"/>
       <c r="K200" s="6"/>
       <c r="M200">
-        <v>1.59</v>
+        <v>1.637</v>
       </c>
     </row>
     <row r="201" spans="1:13" x14ac:dyDescent="0.25">
@@ -8752,7 +8751,7 @@
       <c r="J201" s="6"/>
       <c r="K201" s="6"/>
       <c r="M201">
-        <v>0.91100000000000003</v>
+        <v>0.95799999999999996</v>
       </c>
     </row>
     <row r="202" spans="1:13" x14ac:dyDescent="0.25">
@@ -10702,7 +10701,7 @@
       <c r="J277" s="6"/>
       <c r="K277" s="6"/>
       <c r="M277">
-        <v>2240000</v>
+        <v>2288000</v>
       </c>
     </row>
     <row r="278" spans="1:13" x14ac:dyDescent="0.25">
@@ -10726,7 +10725,7 @@
       <c r="J278" s="6"/>
       <c r="K278" s="6"/>
       <c r="M278">
-        <v>2722000</v>
+        <v>2650000</v>
       </c>
     </row>
     <row r="279" spans="1:13" x14ac:dyDescent="0.25">
@@ -10750,7 +10749,7 @@
       <c r="J279" s="6"/>
       <c r="K279" s="6"/>
       <c r="M279">
-        <v>2420000</v>
+        <v>2498000</v>
       </c>
     </row>
     <row r="280" spans="1:13" x14ac:dyDescent="0.25">
@@ -10774,7 +10773,7 @@
       <c r="J280" s="6"/>
       <c r="K280" s="6"/>
       <c r="M280">
-        <v>1399000</v>
+        <v>1800000</v>
       </c>
     </row>
     <row r="281" spans="1:13" x14ac:dyDescent="0.25">
@@ -10804,7 +10803,7 @@
       <c r="J281" s="6"/>
       <c r="K281" s="6"/>
       <c r="M281">
-        <v>695000</v>
+        <v>723000</v>
       </c>
     </row>
     <row r="282" spans="1:13" x14ac:dyDescent="0.25">
@@ -10934,7 +10933,7 @@
       <c r="J286" s="6"/>
       <c r="K286" s="6"/>
       <c r="M286">
-        <v>57.03</v>
+        <v>60.39</v>
       </c>
     </row>
     <row r="287" spans="1:13" x14ac:dyDescent="0.25">
@@ -10958,7 +10957,7 @@
       <c r="J287" s="6"/>
       <c r="K287" s="6"/>
       <c r="M287">
-        <v>57.76</v>
+        <v>58.34</v>
       </c>
     </row>
     <row r="288" spans="1:13" x14ac:dyDescent="0.25">
@@ -11421,7 +11420,7 @@
       <c r="J305" s="6"/>
       <c r="K305" s="6"/>
       <c r="M305">
-        <v>54.5</v>
+        <v>65.400000000000006</v>
       </c>
     </row>
     <row r="306" spans="1:13" x14ac:dyDescent="0.25">
@@ -12789,7 +12788,7 @@
       <c r="J360" s="6"/>
       <c r="K360" s="6"/>
       <c r="M360">
-        <v>140</v>
+        <v>150</v>
       </c>
     </row>
     <row r="361" spans="1:13" x14ac:dyDescent="0.25">
@@ -12813,7 +12812,7 @@
       <c r="J361" s="6"/>
       <c r="K361" s="6"/>
       <c r="M361">
-        <v>270</v>
+        <v>240</v>
       </c>
     </row>
     <row r="362" spans="1:13" x14ac:dyDescent="0.25">
@@ -12837,7 +12836,7 @@
       <c r="J362" s="6"/>
       <c r="K362" s="6"/>
       <c r="M362">
-        <v>490</v>
+        <v>495</v>
       </c>
     </row>
     <row r="363" spans="1:13" x14ac:dyDescent="0.25">
@@ -12909,7 +12908,7 @@
       <c r="J365" s="6"/>
       <c r="K365" s="6"/>
       <c r="M365">
-        <v>400</v>
+        <v>450</v>
       </c>
     </row>
     <row r="366" spans="1:13" x14ac:dyDescent="0.25">
@@ -12957,7 +12956,7 @@
       <c r="J367" s="6"/>
       <c r="K367" s="6"/>
       <c r="M367">
-        <v>215</v>
+        <v>210</v>
       </c>
     </row>
     <row r="368" spans="1:13" x14ac:dyDescent="0.25">
@@ -12981,7 +12980,7 @@
       <c r="J368" s="6"/>
       <c r="K368" s="6"/>
       <c r="M368">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="369" spans="1:13" x14ac:dyDescent="0.25">
@@ -13005,7 +13004,7 @@
       <c r="J369" s="6"/>
       <c r="K369" s="6"/>
       <c r="M369">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="370" spans="1:13" x14ac:dyDescent="0.25">
@@ -13029,7 +13028,7 @@
       <c r="J370" s="6"/>
       <c r="K370" s="6"/>
       <c r="M370">
-        <v>555</v>
+        <v>650</v>
       </c>
     </row>
     <row r="371" spans="1:13" x14ac:dyDescent="0.25">
@@ -13077,7 +13076,7 @@
       <c r="J372" s="6"/>
       <c r="K372" s="6"/>
       <c r="M372">
-        <v>340</v>
+        <v>370</v>
       </c>
     </row>
     <row r="373" spans="1:13" x14ac:dyDescent="0.25">
@@ -13101,7 +13100,7 @@
       <c r="J373" s="6"/>
       <c r="K373" s="6"/>
       <c r="M373">
-        <v>345</v>
+        <v>360</v>
       </c>
     </row>
     <row r="374" spans="1:13" x14ac:dyDescent="0.25">
@@ -13203,7 +13202,7 @@
       <c r="J377" s="6"/>
       <c r="K377" s="6"/>
       <c r="M377">
-        <v>2500</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="378" spans="1:13" x14ac:dyDescent="0.25">
@@ -13275,7 +13274,7 @@
       <c r="J380" s="6"/>
       <c r="K380" s="6"/>
       <c r="M380">
-        <v>20687</v>
+        <v>23522</v>
       </c>
     </row>
     <row r="381" spans="1:13" x14ac:dyDescent="0.25">
@@ -13361,7 +13360,7 @@
       <c r="J383" s="6"/>
       <c r="K383" s="6"/>
       <c r="M383">
-        <v>45479</v>
+        <v>44733</v>
       </c>
     </row>
     <row r="384" spans="1:13" x14ac:dyDescent="0.25">
@@ -13907,7 +13906,7 @@
       <c r="J405" s="6"/>
       <c r="K405" s="6"/>
       <c r="M405">
-        <v>400</v>
+        <v>500</v>
       </c>
     </row>
     <row r="406" spans="1:13" x14ac:dyDescent="0.25">
@@ -13931,7 +13930,7 @@
       <c r="J406" s="6"/>
       <c r="K406" s="6"/>
       <c r="M406">
-        <v>1000</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="407" spans="1:13" x14ac:dyDescent="0.25">
@@ -13955,7 +13954,7 @@
       <c r="J407" s="6"/>
       <c r="K407" s="6"/>
       <c r="M407">
-        <v>450</v>
+        <v>500</v>
       </c>
     </row>
     <row r="408" spans="1:13" x14ac:dyDescent="0.25">

--- a/TUFE_Konfigurasyon.xlsx
+++ b/TUFE_Konfigurasyon.xlsx
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\vb40890\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\vb41981\Desktop\Fiyat_Veritabani\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F8215E0-1858-4644-9DBB-958C6A4D49AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF596620-7426-4345-93FE-A7D6EB6F416B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Madde_Sepeti" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Madde_Sepeti!$P$1:$P$587</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Madde_Sepeti!$A$1:$M$418</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1478" uniqueCount="1028">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1465" uniqueCount="1022">
   <si>
     <t>Kod</t>
   </si>
@@ -1128,9 +1128,6 @@
     <t>Özel ilkokul ücreti</t>
   </si>
   <si>
-    <t>Özel Lise Ücreti</t>
-  </si>
-  <si>
     <t>Özel lise ücreti</t>
   </si>
   <si>
@@ -1200,12 +1197,6 @@
     <t>Sağlık sigortası</t>
   </si>
   <si>
-    <t>Diş Macunu</t>
-  </si>
-  <si>
-    <t>Şampuan</t>
-  </si>
-  <si>
     <t>Kasko ve zorunlu trafik sigortası</t>
   </si>
   <si>
@@ -2136,9 +2127,6 @@
     <t>https://www.migros.com.tr/signal-white-now-3in1-white-boost-dis-macunu-75-ml-p-2070219</t>
   </si>
   <si>
-    <t>https://www.migros.com.tr/head-shoulders-sampuan-klasik-bakim-2in1-625-ml-p-20a7696</t>
-  </si>
-  <si>
     <t>https://www.cimri.com/kol-saatleri/en-ucuz-casio-f-91w-1dg-erkek-kol-saati-fiyatlari,871635</t>
   </si>
   <si>
@@ -2638,12 +2626,6 @@
   </si>
   <si>
     <t>https://www.carrefoursa.com/artikel-jenerik-karekterler-tuz-boyama-seti-p-30253273?has-promotion</t>
-  </si>
-  <si>
-    <t>https://www.carrefoursa.com/signal-clean-action-3-1-dis-fircasi-p-30244221?has-promotion</t>
-  </si>
-  <si>
-    <t>https://www.carrefoursa.com/head-shoulders-klaslk-bakim-2-si-1-arada-sampuan-250-ml-p-30464167?has-promotion</t>
   </si>
   <si>
     <t>https://www.carrefoursa.com/gillette-blue2-maximum-kullan-at-tiras-bicagi-8-li-p-30077724</t>
@@ -3559,7 +3541,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:O582"/>
+  <dimension ref="A1:O579"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
@@ -3599,16 +3581,16 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>7</v>
@@ -3632,13 +3614,13 @@
         <v>0.23365</v>
       </c>
       <c r="E2" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
@@ -3658,13 +3640,13 @@
         <v>0.23365</v>
       </c>
       <c r="E3" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="J3" s="6"/>
       <c r="K3" s="6"/>
@@ -3684,13 +3666,13 @@
         <v>0.3604</v>
       </c>
       <c r="E4" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
@@ -3710,13 +3692,13 @@
         <v>0.4839</v>
       </c>
       <c r="E5" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="K5" s="6"/>
       <c r="L5" s="6"/>
@@ -3735,13 +3717,13 @@
         <v>0.4839</v>
       </c>
       <c r="E6" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="J6" s="6"/>
       <c r="K6" s="6"/>
@@ -3761,13 +3743,13 @@
         <v>0.4839</v>
       </c>
       <c r="E7" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="J7" s="6"/>
       <c r="K7" s="6"/>
@@ -3787,13 +3769,13 @@
         <v>0.4839</v>
       </c>
       <c r="E8" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="J8" s="6"/>
       <c r="K8" s="6"/>
@@ -3813,13 +3795,13 @@
         <v>0.4839</v>
       </c>
       <c r="E9" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="J9" s="6"/>
       <c r="K9" s="6"/>
@@ -3839,13 +3821,13 @@
         <v>0.4839</v>
       </c>
       <c r="E10" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="J10" s="6"/>
       <c r="K10" s="6"/>
@@ -3865,13 +3847,13 @@
         <v>0.4839</v>
       </c>
       <c r="E11" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="J11" s="6"/>
       <c r="K11" s="6"/>
@@ -3891,13 +3873,13 @@
         <v>2.8400000000000002E-2</v>
       </c>
       <c r="E12" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="J12" s="6"/>
       <c r="K12" s="6"/>
@@ -3917,13 +3899,13 @@
         <v>0.10349999999999999</v>
       </c>
       <c r="E13" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="J13" s="6"/>
       <c r="K13" s="6"/>
@@ -3943,13 +3925,13 @@
         <v>1.2238</v>
       </c>
       <c r="E14" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="J14" s="6"/>
       <c r="K14" s="6"/>
@@ -3969,13 +3951,13 @@
         <v>1.2238</v>
       </c>
       <c r="E15" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="J15" s="6"/>
       <c r="K15" s="6"/>
@@ -3995,13 +3977,13 @@
         <v>1.2238</v>
       </c>
       <c r="E16" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="J16" s="6"/>
       <c r="K16" s="6"/>
@@ -4021,13 +4003,13 @@
         <v>8.0699999999999994E-2</v>
       </c>
       <c r="E17" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="J17" s="6"/>
       <c r="K17" s="6"/>
@@ -4047,13 +4029,13 @@
         <v>8.0699999999999994E-2</v>
       </c>
       <c r="E18" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="J18" s="6"/>
       <c r="K18" s="6"/>
@@ -4073,13 +4055,13 @@
         <v>8.0699999999999994E-2</v>
       </c>
       <c r="E19" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="J19" s="6"/>
       <c r="K19" s="6"/>
@@ -4099,13 +4081,13 @@
         <v>0.11360000000000001</v>
       </c>
       <c r="E20" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="J20" s="6"/>
       <c r="K20" s="6"/>
@@ -4125,13 +4107,13 @@
         <v>0.11360000000000001</v>
       </c>
       <c r="E21" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="J21" s="6"/>
       <c r="K21" s="6"/>
@@ -4151,13 +4133,13 @@
         <v>0.11360000000000001</v>
       </c>
       <c r="E22" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="J22" s="6"/>
       <c r="K22" s="6"/>
@@ -4177,13 +4159,13 @@
         <v>3.6900000000000002E-2</v>
       </c>
       <c r="E23" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="J23" s="6"/>
       <c r="K23" s="6"/>
@@ -4203,13 +4185,13 @@
         <v>0.5202</v>
       </c>
       <c r="E24" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="J24" s="6"/>
       <c r="K24" s="6"/>
@@ -4229,13 +4211,13 @@
         <v>5.57E-2</v>
       </c>
       <c r="E25" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="J25" s="6"/>
       <c r="K25" s="6"/>
@@ -4255,13 +4237,13 @@
         <v>5.3100000000000001E-2</v>
       </c>
       <c r="E26" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="J26" s="6"/>
       <c r="K26" s="6"/>
@@ -4281,13 +4263,13 @@
         <v>0.2994</v>
       </c>
       <c r="E27" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="J27" s="6"/>
       <c r="K27" s="6"/>
@@ -4307,13 +4289,13 @@
         <v>0.2994</v>
       </c>
       <c r="E28" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="J28" s="6"/>
       <c r="K28" s="6"/>
@@ -4333,13 +4315,13 @@
         <v>0.2994</v>
       </c>
       <c r="E29" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="J29" s="6"/>
       <c r="K29" s="6"/>
@@ -4359,13 +4341,13 @@
         <v>0.2994</v>
       </c>
       <c r="E30" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="J30" s="6"/>
       <c r="K30" s="6"/>
@@ -4385,13 +4367,13 @@
         <v>0.2455</v>
       </c>
       <c r="E31" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="J31" s="6"/>
       <c r="K31" s="6"/>
@@ -4411,13 +4393,13 @@
         <v>0.2455</v>
       </c>
       <c r="E32" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="J32" s="6"/>
       <c r="K32" s="6"/>
@@ -4437,13 +4419,13 @@
         <v>2.8899999999999999E-2</v>
       </c>
       <c r="E33" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="J33" s="6"/>
       <c r="K33" s="6"/>
@@ -4463,13 +4445,13 @@
         <v>2.8899999999999999E-2</v>
       </c>
       <c r="E34" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="J34" s="6"/>
       <c r="K34" s="6"/>
@@ -4489,13 +4471,13 @@
         <v>0.60060000000000002</v>
       </c>
       <c r="E35" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="J35" s="6"/>
       <c r="K35" s="6"/>
@@ -4515,13 +4497,13 @@
         <v>0.49809999999999999</v>
       </c>
       <c r="E36" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="J36" s="6"/>
       <c r="K36" s="6"/>
@@ -4541,13 +4523,13 @@
         <v>0.49809999999999999</v>
       </c>
       <c r="E37" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="J37" s="6"/>
       <c r="K37" s="6"/>
@@ -4567,13 +4549,13 @@
         <v>0.3332</v>
       </c>
       <c r="E38" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="J38" s="6"/>
       <c r="K38" s="6"/>
@@ -4593,13 +4575,13 @@
         <v>0.24129999999999999</v>
       </c>
       <c r="E39" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="J39" s="6"/>
       <c r="K39" s="6"/>
@@ -4619,13 +4601,13 @@
         <v>8.9800000000000005E-2</v>
       </c>
       <c r="E40" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="J40" s="6"/>
       <c r="K40" s="6"/>
@@ -4645,13 +4627,13 @@
         <v>8.9800000000000005E-2</v>
       </c>
       <c r="E41" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="J41" s="6"/>
       <c r="K41" s="6"/>
@@ -4671,13 +4653,13 @@
         <v>8.9800000000000005E-2</v>
       </c>
       <c r="E42" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="J42" s="6"/>
       <c r="K42" s="6"/>
@@ -4697,13 +4679,13 @@
         <v>0.1686</v>
       </c>
       <c r="E43" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="J43" s="6"/>
       <c r="K43" s="6"/>
@@ -4723,13 +4705,13 @@
         <v>0.1686</v>
       </c>
       <c r="E44" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="J44" s="6"/>
       <c r="K44" s="6"/>
@@ -4749,13 +4731,13 @@
         <v>0.1686</v>
       </c>
       <c r="E45" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="J45" s="6"/>
       <c r="K45" s="6"/>
@@ -4775,13 +4757,13 @@
         <v>5.6099999999999997E-2</v>
       </c>
       <c r="E46" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="J46" s="6"/>
       <c r="K46" s="6"/>
@@ -4801,13 +4783,13 @@
         <v>7.2300000000000003E-2</v>
       </c>
       <c r="E47" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="J47" s="6"/>
       <c r="K47" s="6"/>
@@ -4827,13 +4809,13 @@
         <v>7.2300000000000003E-2</v>
       </c>
       <c r="E48" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="J48" s="6"/>
       <c r="K48" s="6"/>
@@ -4853,13 +4835,13 @@
         <v>7.2300000000000003E-2</v>
       </c>
       <c r="E49" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="J49" s="6"/>
       <c r="K49" s="6"/>
@@ -4879,13 +4861,13 @@
         <v>7.2300000000000003E-2</v>
       </c>
       <c r="E50" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="J50" s="6"/>
       <c r="K50" s="6"/>
@@ -4905,13 +4887,13 @@
         <v>7.2300000000000003E-2</v>
       </c>
       <c r="E51" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="J51" s="6"/>
       <c r="K51" s="6"/>
@@ -4931,13 +4913,13 @@
         <v>3.6999999999999998E-2</v>
       </c>
       <c r="E52" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="I52" s="6" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="J52" s="6"/>
       <c r="K52" s="6"/>
@@ -4957,13 +4939,13 @@
         <v>3.6999999999999998E-2</v>
       </c>
       <c r="E53" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="I53" s="6" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="J53" s="6"/>
       <c r="K53" s="6"/>
@@ -4983,13 +4965,13 @@
         <v>3.6999999999999998E-2</v>
       </c>
       <c r="E54" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="J54" s="6"/>
       <c r="K54" s="6"/>
@@ -5009,13 +4991,13 @@
         <v>0.1244</v>
       </c>
       <c r="E55" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="I55" s="6" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="J55" s="6"/>
       <c r="K55" s="6"/>
@@ -5035,13 +5017,13 @@
         <v>0.1244</v>
       </c>
       <c r="E56" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="I56" s="6" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="J56" s="6"/>
       <c r="K56" s="6"/>
@@ -5061,13 +5043,13 @@
         <v>0.1244</v>
       </c>
       <c r="E57" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="I57" s="6" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
       <c r="J57" s="6"/>
       <c r="K57" s="6"/>
@@ -5087,13 +5069,13 @@
         <v>0.1244</v>
       </c>
       <c r="E58" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="I58" s="6" t="s">
-        <v>790</v>
+        <v>786</v>
       </c>
       <c r="J58" s="6"/>
       <c r="K58" s="6"/>
@@ -5113,13 +5095,13 @@
         <v>0.1244</v>
       </c>
       <c r="E59" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="I59" s="6" t="s">
-        <v>791</v>
+        <v>787</v>
       </c>
       <c r="J59" s="6"/>
       <c r="K59" s="6"/>
@@ -5139,13 +5121,13 @@
         <v>0.1244</v>
       </c>
       <c r="E60" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="I60" s="6" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
       <c r="J60" s="6"/>
       <c r="K60" s="6"/>
@@ -5165,13 +5147,13 @@
         <v>0.1244</v>
       </c>
       <c r="E61" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="I61" s="6" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
       <c r="J61" s="6"/>
       <c r="K61" s="6"/>
@@ -5191,13 +5173,13 @@
         <v>0.1244</v>
       </c>
       <c r="E62" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="I62" s="6" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
       <c r="J62" s="6"/>
       <c r="K62" s="6"/>
@@ -5217,13 +5199,13 @@
         <v>5.3900000000000003E-2</v>
       </c>
       <c r="E63" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="I63" s="6" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
       <c r="J63" s="6"/>
       <c r="K63" s="6"/>
@@ -5243,13 +5225,13 @@
         <v>5.3900000000000003E-2</v>
       </c>
       <c r="E64" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="I64" s="6" t="s">
-        <v>796</v>
+        <v>792</v>
       </c>
       <c r="J64" s="6"/>
       <c r="K64" s="6"/>
@@ -5269,13 +5251,13 @@
         <v>5.3900000000000003E-2</v>
       </c>
       <c r="E65" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="I65" s="6" t="s">
-        <v>797</v>
+        <v>793</v>
       </c>
       <c r="J65" s="6"/>
       <c r="K65" s="6"/>
@@ -5295,13 +5277,13 @@
         <v>5.3900000000000003E-2</v>
       </c>
       <c r="E66" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="I66" s="6" t="s">
-        <v>798</v>
+        <v>794</v>
       </c>
       <c r="J66" s="6"/>
       <c r="K66" s="6"/>
@@ -5321,13 +5303,13 @@
         <v>0.22170000000000001</v>
       </c>
       <c r="E67" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H67" s="6" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="I67" s="6" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
       <c r="J67" s="6"/>
       <c r="K67" s="6"/>
@@ -5347,13 +5329,13 @@
         <v>0.22170000000000001</v>
       </c>
       <c r="E68" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="I68" s="6" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="J68" s="6"/>
       <c r="K68" s="6"/>
@@ -5373,13 +5355,13 @@
         <v>0.22170000000000001</v>
       </c>
       <c r="E69" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H69" s="6" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="I69" s="6" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="J69" s="6"/>
       <c r="K69" s="6"/>
@@ -5399,13 +5381,13 @@
         <v>0.22170000000000001</v>
       </c>
       <c r="E70" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="I70" s="6" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="J70" s="6"/>
       <c r="K70" s="6"/>
@@ -5425,13 +5407,13 @@
         <v>0.22170000000000001</v>
       </c>
       <c r="E71" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H71" s="6" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="I71" s="6" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="J71" s="6"/>
       <c r="K71" s="6"/>
@@ -5451,13 +5433,13 @@
         <v>0.22170000000000001</v>
       </c>
       <c r="E72" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="I72" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="J72" s="6"/>
       <c r="K72" s="6"/>
@@ -5477,13 +5459,13 @@
         <v>0.1487</v>
       </c>
       <c r="E73" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H73" s="6" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="I73" s="6" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="J73" s="6"/>
       <c r="K73" s="6"/>
@@ -5503,13 +5485,13 @@
         <v>0.1057</v>
       </c>
       <c r="E74" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="I74" s="6" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="J74" s="6"/>
       <c r="K74" s="6"/>
@@ -5529,13 +5511,13 @@
         <v>0.1057</v>
       </c>
       <c r="E75" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="I75" s="6" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="J75" s="6"/>
       <c r="K75" s="6"/>
@@ -5555,13 +5537,13 @@
         <v>0.1057</v>
       </c>
       <c r="E76" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="I76" s="6" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="J76" s="6"/>
       <c r="K76" s="6"/>
@@ -5581,13 +5563,13 @@
         <v>0.1057</v>
       </c>
       <c r="E77" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="I77" s="6" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="J77" s="6"/>
       <c r="K77" s="6"/>
@@ -5607,13 +5589,13 @@
         <v>0.1057</v>
       </c>
       <c r="E78" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="I78" s="6" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="J78" s="6"/>
       <c r="K78" s="6"/>
@@ -5633,13 +5615,13 @@
         <v>0.1057</v>
       </c>
       <c r="E79" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="I79" s="6" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J79" s="6"/>
       <c r="K79" s="6"/>
@@ -5659,13 +5641,13 @@
         <v>0.1057</v>
       </c>
       <c r="E80" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="I80" s="6" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="J80" s="6"/>
       <c r="K80" s="6"/>
@@ -5685,13 +5667,13 @@
         <v>0.35189999999999999</v>
       </c>
       <c r="E81" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H81" s="6" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="I81" s="6" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="J81" s="6"/>
       <c r="K81" s="6"/>
@@ -5711,13 +5693,13 @@
         <v>7.2400000000000006E-2</v>
       </c>
       <c r="E82" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="I82" s="6" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="J82" s="6"/>
       <c r="K82" s="6"/>
@@ -5737,13 +5719,13 @@
         <v>7.2400000000000006E-2</v>
       </c>
       <c r="E83" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H83" s="6" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="I83" s="6" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
       <c r="J83" s="6"/>
       <c r="K83" s="6"/>
@@ -5763,13 +5745,13 @@
         <v>7.2400000000000006E-2</v>
       </c>
       <c r="E84" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="I84" s="6" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="J84" s="6"/>
       <c r="K84" s="6"/>
@@ -5789,13 +5771,13 @@
         <v>0.10970000000000001</v>
       </c>
       <c r="E85" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H85" s="6" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="I85" s="6" t="s">
-        <v>817</v>
+        <v>813</v>
       </c>
       <c r="J85" s="6"/>
       <c r="K85" s="6"/>
@@ -5815,13 +5797,13 @@
         <v>0.10970000000000001</v>
       </c>
       <c r="E86" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="I86" s="6" t="s">
-        <v>818</v>
+        <v>814</v>
       </c>
       <c r="J86" s="6"/>
       <c r="K86" s="6"/>
@@ -5841,13 +5823,13 @@
         <v>0.10970000000000001</v>
       </c>
       <c r="E87" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H87" s="6" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="I87" s="6" t="s">
-        <v>819</v>
+        <v>815</v>
       </c>
       <c r="J87" s="6"/>
       <c r="K87" s="6"/>
@@ -5867,13 +5849,13 @@
         <v>0.10970000000000001</v>
       </c>
       <c r="E88" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="I88" s="6" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
       <c r="J88" s="6"/>
       <c r="K88" s="6"/>
@@ -5893,13 +5875,13 @@
         <v>0.1772</v>
       </c>
       <c r="E89" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H89" s="6" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="I89" s="6" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
       <c r="J89" s="6"/>
       <c r="K89" s="6"/>
@@ -5919,13 +5901,13 @@
         <v>0.1772</v>
       </c>
       <c r="E90" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="I90" s="6" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
       <c r="J90" s="6"/>
       <c r="K90" s="6"/>
@@ -5945,13 +5927,13 @@
         <v>9.5899999999999999E-2</v>
       </c>
       <c r="E91" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H91" s="6" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="I91" s="6" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="J91" s="6"/>
       <c r="K91" s="6"/>
@@ -5971,13 +5953,13 @@
         <v>9.5899999999999999E-2</v>
       </c>
       <c r="E92" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="I92" s="6" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
       <c r="J92" s="6"/>
       <c r="K92" s="6"/>
@@ -5997,13 +5979,13 @@
         <v>9.5899999999999999E-2</v>
       </c>
       <c r="E93" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H93" s="6" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="I93" s="6" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="J93" s="6"/>
       <c r="K93" s="6"/>
@@ -6023,13 +6005,13 @@
         <v>3.2099999999999997E-2</v>
       </c>
       <c r="E94" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="I94" s="6" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="J94" s="6"/>
       <c r="K94" s="6"/>
@@ -6049,13 +6031,13 @@
         <v>0.1754</v>
       </c>
       <c r="E95" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H95" s="6" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="I95" s="6" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="J95" s="6"/>
       <c r="K95" s="6"/>
@@ -6075,13 +6057,13 @@
         <v>0.1754</v>
       </c>
       <c r="E96" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="I96" s="6" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
       <c r="J96" s="6"/>
       <c r="K96" s="6"/>
@@ -6101,13 +6083,13 @@
         <v>0.21329999999999999</v>
       </c>
       <c r="E97" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H97" s="6" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="I97" s="6" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="J97" s="6"/>
       <c r="K97" s="6"/>
@@ -6127,13 +6109,13 @@
         <v>6.3700000000000007E-2</v>
       </c>
       <c r="E98" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="I98" s="6" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="J98" s="6"/>
       <c r="K98" s="6"/>
@@ -6153,13 +6135,13 @@
         <v>6.3700000000000007E-2</v>
       </c>
       <c r="E99" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H99" s="6" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="I99" s="6" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="J99" s="6"/>
       <c r="K99" s="6"/>
@@ -6179,13 +6161,13 @@
         <v>6.3700000000000007E-2</v>
       </c>
       <c r="E100" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="I100" s="6" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
       <c r="J100" s="6"/>
       <c r="K100" s="6"/>
@@ -6205,13 +6187,13 @@
         <v>6.3700000000000007E-2</v>
       </c>
       <c r="E101" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H101" s="6" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="I101" s="6" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="J101" s="6"/>
       <c r="K101" s="6"/>
@@ -6231,13 +6213,13 @@
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="E102" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="I102" s="6" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="J102" s="6"/>
       <c r="K102" s="6"/>
@@ -6257,13 +6239,13 @@
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="E103" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H103" s="6" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="I103" s="6" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="J103" s="6"/>
       <c r="K103" s="6"/>
@@ -6283,13 +6265,13 @@
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="E104" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="I104" s="6" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
       <c r="J104" s="6"/>
       <c r="K104" s="6"/>
@@ -6309,13 +6291,13 @@
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="E105" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H105" s="6" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="I105" s="6" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
       <c r="J105" s="6"/>
       <c r="K105" s="6"/>
@@ -6335,13 +6317,13 @@
         <v>8.77E-2</v>
       </c>
       <c r="E106" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="I106" s="6" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
       <c r="J106" s="6"/>
       <c r="K106" s="6"/>
@@ -6361,13 +6343,13 @@
         <v>3.2899999999999999E-2</v>
       </c>
       <c r="E107" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H107" s="6" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="I107" s="6" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="J107" s="6"/>
       <c r="K107" s="6"/>
@@ -6387,13 +6369,13 @@
         <v>3.2899999999999999E-2</v>
       </c>
       <c r="E108" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="I108" s="6" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="J108" s="6"/>
       <c r="K108" s="6"/>
@@ -6413,13 +6395,13 @@
         <v>3.2899999999999999E-2</v>
       </c>
       <c r="E109" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H109" s="6" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="I109" s="6" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
       <c r="J109" s="6"/>
       <c r="K109" s="6"/>
@@ -6439,13 +6421,13 @@
         <v>3.2899999999999999E-2</v>
       </c>
       <c r="E110" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="I110" s="6" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="J110" s="6"/>
       <c r="K110" s="6"/>
@@ -6465,13 +6447,13 @@
         <v>8.77E-2</v>
       </c>
       <c r="E111" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H111" s="6" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="I111" s="6" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="J111" s="6"/>
       <c r="K111" s="6"/>
@@ -6491,13 +6473,13 @@
         <v>8.77E-2</v>
       </c>
       <c r="E112" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="I112" s="6" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="J112" s="6"/>
       <c r="K112" s="6"/>
@@ -6517,13 +6499,13 @@
         <v>3.4700000000000002E-2</v>
       </c>
       <c r="E113" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H113" s="6" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="I113" s="6" t="s">
-        <v>845</v>
+        <v>841</v>
       </c>
       <c r="J113" s="6"/>
       <c r="K113" s="6"/>
@@ -6543,13 +6525,13 @@
         <v>3.4700000000000002E-2</v>
       </c>
       <c r="E114" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="I114" s="6" t="s">
-        <v>846</v>
+        <v>842</v>
       </c>
       <c r="J114" s="6"/>
       <c r="K114" s="6"/>
@@ -6569,13 +6551,13 @@
         <v>0.1832</v>
       </c>
       <c r="E115" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H115" s="6" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="I115" s="6" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="J115" s="6"/>
       <c r="K115" s="6"/>
@@ -6595,13 +6577,13 @@
         <v>0.1686</v>
       </c>
       <c r="E116" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="I116" s="6" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="J116" s="6"/>
       <c r="K116" s="6"/>
@@ -6621,13 +6603,13 @@
         <v>0.1686</v>
       </c>
       <c r="E117" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H117" s="6" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="I117" s="6" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="J117" s="6"/>
       <c r="K117" s="6"/>
@@ -6647,13 +6629,13 @@
         <v>0.35249999999999998</v>
       </c>
       <c r="E118" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="I118" s="6" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
       <c r="J118" s="6"/>
       <c r="K118" s="6"/>
@@ -6673,13 +6655,13 @@
         <v>0.35249999999999998</v>
       </c>
       <c r="E119" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H119" s="6" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="I119" s="6" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
       <c r="J119" s="6"/>
       <c r="K119" s="6"/>
@@ -6699,13 +6681,13 @@
         <v>0.29770000000000002</v>
       </c>
       <c r="E120" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="I120" s="6" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="J120" s="6"/>
       <c r="K120" s="6"/>
@@ -6725,13 +6707,13 @@
         <v>0.29770000000000002</v>
       </c>
       <c r="E121" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H121" s="6" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="I121" s="6" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
       <c r="J121" s="6"/>
       <c r="K121" s="6"/>
@@ -6751,13 +6733,13 @@
         <v>0.25969999999999999</v>
       </c>
       <c r="E122" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="I122" s="6" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
       <c r="J122" s="6"/>
       <c r="K122" s="6"/>
@@ -6777,13 +6759,13 @@
         <v>0.25969999999999999</v>
       </c>
       <c r="E123" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H123" s="6" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="I123" s="6" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
       <c r="J123" s="6"/>
       <c r="K123" s="6"/>
@@ -6803,7 +6785,7 @@
         <v>0.13900000000000001</v>
       </c>
       <c r="E124" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="H124" s="6"/>
       <c r="I124" s="6"/>
@@ -6828,7 +6810,7 @@
         <v>6.9500000000000006E-2</v>
       </c>
       <c r="E125" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="H125" s="6"/>
       <c r="I125" s="6"/>
@@ -6853,7 +6835,7 @@
         <v>6.9500000000000006E-2</v>
       </c>
       <c r="E126" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="H126" s="6"/>
       <c r="I126" s="6"/>
@@ -6878,7 +6860,7 @@
         <v>4.7800000000000002E-2</v>
       </c>
       <c r="E127" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="H127" s="6"/>
       <c r="I127" s="6"/>
@@ -6903,7 +6885,7 @@
         <v>0.27179999999999999</v>
       </c>
       <c r="E128" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="H128" s="6"/>
       <c r="I128" s="6"/>
@@ -6928,7 +6910,7 @@
         <v>2.1572</v>
       </c>
       <c r="E129" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="H129" s="6"/>
       <c r="I129" s="6"/>
@@ -6952,15 +6934,15 @@
         <v>0.23549999999999999</v>
       </c>
       <c r="E130" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H130" s="6"/>
       <c r="I130" s="6"/>
       <c r="J130" s="6" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="K130" s="6" t="s">
-        <v>876</v>
+        <v>870</v>
       </c>
     </row>
     <row r="131" spans="1:13" x14ac:dyDescent="0.25">
@@ -6977,15 +6959,15 @@
         <v>0.23549999999999999</v>
       </c>
       <c r="E131" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H131" s="6"/>
       <c r="I131" s="6"/>
       <c r="J131" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="K131" s="6" t="s">
-        <v>877</v>
+        <v>871</v>
       </c>
     </row>
     <row r="132" spans="1:13" x14ac:dyDescent="0.25">
@@ -7002,15 +6984,15 @@
         <v>0.23549999999999999</v>
       </c>
       <c r="E132" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H132" s="6"/>
       <c r="I132" s="6"/>
       <c r="J132" s="6" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="K132" s="6" t="s">
-        <v>878</v>
+        <v>872</v>
       </c>
     </row>
     <row r="133" spans="1:13" x14ac:dyDescent="0.25">
@@ -7027,15 +7009,15 @@
         <v>0.23549999999999999</v>
       </c>
       <c r="E133" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H133" s="6"/>
       <c r="I133" s="6"/>
       <c r="J133" s="6" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="K133" s="6" t="s">
-        <v>879</v>
+        <v>873</v>
       </c>
     </row>
     <row r="134" spans="1:13" x14ac:dyDescent="0.25">
@@ -7052,15 +7034,15 @@
         <v>0.23549999999999999</v>
       </c>
       <c r="E134" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H134" s="6"/>
       <c r="I134" s="6"/>
       <c r="J134" s="6" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="K134" s="6" t="s">
-        <v>880</v>
+        <v>874</v>
       </c>
     </row>
     <row r="135" spans="1:13" x14ac:dyDescent="0.25">
@@ -7077,15 +7059,15 @@
         <v>0.23549999999999999</v>
       </c>
       <c r="E135" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H135" s="6"/>
       <c r="I135" s="6"/>
       <c r="J135" s="6" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="K135" s="6" t="s">
-        <v>881</v>
+        <v>875</v>
       </c>
     </row>
     <row r="136" spans="1:13" x14ac:dyDescent="0.25">
@@ -7102,15 +7084,15 @@
         <v>0.23549999999999999</v>
       </c>
       <c r="E136" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H136" s="6"/>
       <c r="I136" s="6"/>
       <c r="J136" s="6" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="K136" s="6" t="s">
-        <v>882</v>
+        <v>876</v>
       </c>
     </row>
     <row r="137" spans="1:13" x14ac:dyDescent="0.25">
@@ -7127,15 +7109,15 @@
         <v>0.23549999999999999</v>
       </c>
       <c r="E137" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H137" s="6"/>
       <c r="I137" s="6"/>
       <c r="J137" s="6" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="K137" s="6" t="s">
-        <v>883</v>
+        <v>877</v>
       </c>
     </row>
     <row r="138" spans="1:13" x14ac:dyDescent="0.25">
@@ -7152,15 +7134,15 @@
         <v>0.23549999999999999</v>
       </c>
       <c r="E138" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H138" s="6"/>
       <c r="I138" s="6"/>
       <c r="J138" s="6" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="K138" s="6" t="s">
-        <v>884</v>
+        <v>878</v>
       </c>
     </row>
     <row r="139" spans="1:13" x14ac:dyDescent="0.25">
@@ -7177,15 +7159,15 @@
         <v>0.23549999999999999</v>
       </c>
       <c r="E139" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H139" s="6"/>
       <c r="I139" s="6"/>
       <c r="J139" s="6" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="K139" s="6" t="s">
-        <v>885</v>
+        <v>879</v>
       </c>
     </row>
     <row r="140" spans="1:13" x14ac:dyDescent="0.25">
@@ -7202,15 +7184,15 @@
         <v>0.23549999999999999</v>
       </c>
       <c r="E140" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H140" s="6"/>
       <c r="I140" s="6"/>
       <c r="J140" s="6" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="K140" s="6" t="s">
-        <v>886</v>
+        <v>880</v>
       </c>
     </row>
     <row r="141" spans="1:13" x14ac:dyDescent="0.25">
@@ -7227,15 +7209,15 @@
         <v>0.23549999999999999</v>
       </c>
       <c r="E141" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H141" s="6"/>
       <c r="I141" s="6"/>
       <c r="J141" s="6" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="K141" s="6" t="s">
-        <v>887</v>
+        <v>881</v>
       </c>
     </row>
     <row r="142" spans="1:13" x14ac:dyDescent="0.25">
@@ -7252,15 +7234,15 @@
         <v>0.23549999999999999</v>
       </c>
       <c r="E142" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H142" s="6"/>
       <c r="I142" s="6"/>
       <c r="J142" s="6" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="K142" s="6" t="s">
-        <v>888</v>
+        <v>882</v>
       </c>
     </row>
     <row r="143" spans="1:13" x14ac:dyDescent="0.25">
@@ -7277,15 +7259,15 @@
         <v>0.1351</v>
       </c>
       <c r="E143" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H143" s="6"/>
       <c r="I143" s="6"/>
       <c r="J143" s="6" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="K143" s="6" t="s">
-        <v>889</v>
+        <v>883</v>
       </c>
     </row>
     <row r="144" spans="1:13" x14ac:dyDescent="0.25">
@@ -7302,15 +7284,15 @@
         <v>0.1351</v>
       </c>
       <c r="E144" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H144" s="6"/>
       <c r="I144" s="6"/>
       <c r="J144" s="6" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="K144" s="6" t="s">
-        <v>890</v>
+        <v>884</v>
       </c>
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.25">
@@ -7327,15 +7309,15 @@
         <v>0.1351</v>
       </c>
       <c r="E145" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H145" s="6"/>
       <c r="I145" s="6"/>
       <c r="J145" s="6" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="K145" s="6" t="s">
-        <v>891</v>
+        <v>885</v>
       </c>
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.25">
@@ -7352,15 +7334,15 @@
         <v>0.1351</v>
       </c>
       <c r="E146" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H146" s="6"/>
       <c r="I146" s="6"/>
       <c r="J146" s="6" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="K146" s="6" t="s">
-        <v>892</v>
+        <v>886</v>
       </c>
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.25">
@@ -7377,15 +7359,15 @@
         <v>0.1351</v>
       </c>
       <c r="E147" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H147" s="6"/>
       <c r="I147" s="6"/>
       <c r="J147" s="6" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="K147" s="6" t="s">
-        <v>893</v>
+        <v>887</v>
       </c>
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.25">
@@ -7402,15 +7384,15 @@
         <v>0.1351</v>
       </c>
       <c r="E148" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H148" s="6"/>
       <c r="I148" s="6"/>
       <c r="J148" s="6" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="K148" s="6" t="s">
-        <v>894</v>
+        <v>888</v>
       </c>
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.25">
@@ -7427,15 +7409,15 @@
         <v>0.1351</v>
       </c>
       <c r="E149" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H149" s="6"/>
       <c r="I149" s="6"/>
       <c r="J149" s="6" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="K149" s="6" t="s">
-        <v>895</v>
+        <v>889</v>
       </c>
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.25">
@@ -7452,15 +7434,15 @@
         <v>0.1351</v>
       </c>
       <c r="E150" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H150" s="6"/>
       <c r="I150" s="6"/>
       <c r="J150" s="6" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="K150" s="6" t="s">
-        <v>896</v>
+        <v>890</v>
       </c>
     </row>
     <row r="151" spans="1:11" x14ac:dyDescent="0.25">
@@ -7477,15 +7459,15 @@
         <v>0.2278</v>
       </c>
       <c r="E151" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H151" s="6"/>
       <c r="I151" s="6"/>
       <c r="J151" s="6" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="K151" s="6" t="s">
-        <v>897</v>
+        <v>891</v>
       </c>
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.25">
@@ -7502,15 +7484,15 @@
         <v>0.2278</v>
       </c>
       <c r="E152" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H152" s="6"/>
       <c r="I152" s="6"/>
       <c r="J152" s="6" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="K152" s="6" t="s">
-        <v>898</v>
+        <v>892</v>
       </c>
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.25">
@@ -7527,15 +7509,15 @@
         <v>0.2278</v>
       </c>
       <c r="E153" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H153" s="6"/>
       <c r="I153" s="6"/>
       <c r="J153" s="6" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="K153" s="6" t="s">
-        <v>899</v>
+        <v>893</v>
       </c>
     </row>
     <row r="154" spans="1:11" x14ac:dyDescent="0.25">
@@ -7552,15 +7534,15 @@
         <v>0.2278</v>
       </c>
       <c r="E154" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H154" s="6"/>
       <c r="I154" s="6"/>
       <c r="J154" s="6" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="K154" s="6" t="s">
-        <v>900</v>
+        <v>894</v>
       </c>
     </row>
     <row r="155" spans="1:11" x14ac:dyDescent="0.25">
@@ -7577,15 +7559,15 @@
         <v>0.2278</v>
       </c>
       <c r="E155" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H155" s="6"/>
       <c r="I155" s="6"/>
       <c r="J155" s="6" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="K155" s="6" t="s">
-        <v>901</v>
+        <v>895</v>
       </c>
     </row>
     <row r="156" spans="1:11" x14ac:dyDescent="0.25">
@@ -7602,15 +7584,15 @@
         <v>0.2278</v>
       </c>
       <c r="E156" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H156" s="6"/>
       <c r="I156" s="6"/>
       <c r="J156" s="6" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="K156" s="6" t="s">
-        <v>902</v>
+        <v>896</v>
       </c>
     </row>
     <row r="157" spans="1:11" x14ac:dyDescent="0.25">
@@ -7627,15 +7609,15 @@
         <v>0.2278</v>
       </c>
       <c r="E157" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H157" s="6"/>
       <c r="I157" s="6"/>
       <c r="J157" s="6" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="K157" s="6" t="s">
-        <v>903</v>
+        <v>897</v>
       </c>
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.25">
@@ -7652,15 +7634,15 @@
         <v>0.2278</v>
       </c>
       <c r="E158" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H158" s="6"/>
       <c r="I158" s="6"/>
       <c r="J158" s="6" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="K158" s="6" t="s">
-        <v>904</v>
+        <v>898</v>
       </c>
     </row>
     <row r="159" spans="1:11" x14ac:dyDescent="0.25">
@@ -7677,15 +7659,15 @@
         <v>0.2278</v>
       </c>
       <c r="E159" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H159" s="6"/>
       <c r="I159" s="6"/>
       <c r="J159" s="6" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="K159" s="6" t="s">
-        <v>905</v>
+        <v>899</v>
       </c>
     </row>
     <row r="160" spans="1:11" x14ac:dyDescent="0.25">
@@ -7702,15 +7684,15 @@
         <v>0.2278</v>
       </c>
       <c r="E160" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H160" s="6"/>
       <c r="I160" s="6"/>
       <c r="J160" s="6" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="K160" s="6" t="s">
-        <v>906</v>
+        <v>900</v>
       </c>
     </row>
     <row r="161" spans="1:11" x14ac:dyDescent="0.25">
@@ -7727,15 +7709,15 @@
         <v>0.2278</v>
       </c>
       <c r="E161" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H161" s="6"/>
       <c r="I161" s="6"/>
       <c r="J161" s="6" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="K161" t="s">
-        <v>908</v>
+        <v>902</v>
       </c>
     </row>
     <row r="162" spans="1:11" x14ac:dyDescent="0.25">
@@ -7752,15 +7734,15 @@
         <v>0.2278</v>
       </c>
       <c r="E162" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H162" s="6"/>
       <c r="I162" s="6"/>
       <c r="J162" s="6" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="K162" s="6" t="s">
-        <v>907</v>
+        <v>901</v>
       </c>
     </row>
     <row r="163" spans="1:11" x14ac:dyDescent="0.25">
@@ -7777,15 +7759,15 @@
         <v>0.2278</v>
       </c>
       <c r="E163" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H163" s="6"/>
       <c r="I163" s="6"/>
       <c r="J163" s="6" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="K163" s="6" t="s">
-        <v>909</v>
+        <v>903</v>
       </c>
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.25">
@@ -7802,15 +7784,15 @@
         <v>0.2278</v>
       </c>
       <c r="E164" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H164" s="6"/>
       <c r="I164" s="6"/>
       <c r="J164" s="6" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="K164" s="6" t="s">
-        <v>910</v>
+        <v>904</v>
       </c>
     </row>
     <row r="165" spans="1:11" x14ac:dyDescent="0.25">
@@ -7827,15 +7809,15 @@
         <v>0.2278</v>
       </c>
       <c r="E165" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H165" s="6"/>
       <c r="I165" s="6"/>
       <c r="J165" s="6" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="K165" s="6" t="s">
-        <v>911</v>
+        <v>905</v>
       </c>
     </row>
     <row r="166" spans="1:11" x14ac:dyDescent="0.25">
@@ -7852,15 +7834,15 @@
         <v>0.1351</v>
       </c>
       <c r="E166" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H166" s="6"/>
       <c r="I166" s="6"/>
       <c r="J166" s="6" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="K166" s="6" t="s">
-        <v>912</v>
+        <v>906</v>
       </c>
     </row>
     <row r="167" spans="1:11" x14ac:dyDescent="0.25">
@@ -7877,15 +7859,15 @@
         <v>0.1351</v>
       </c>
       <c r="E167" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H167" s="6"/>
       <c r="I167" s="6"/>
       <c r="J167" s="6" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="K167" s="6" t="s">
-        <v>913</v>
+        <v>907</v>
       </c>
     </row>
     <row r="168" spans="1:11" x14ac:dyDescent="0.25">
@@ -7902,15 +7884,15 @@
         <v>0.1351</v>
       </c>
       <c r="E168" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H168" s="6"/>
       <c r="I168" s="6"/>
       <c r="J168" s="6" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="K168" s="6" t="s">
-        <v>914</v>
+        <v>908</v>
       </c>
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.25">
@@ -7927,15 +7909,15 @@
         <v>0.1351</v>
       </c>
       <c r="E169" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H169" s="6"/>
       <c r="I169" s="6"/>
       <c r="J169" s="6" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="K169" s="6" t="s">
-        <v>915</v>
+        <v>909</v>
       </c>
     </row>
     <row r="170" spans="1:11" x14ac:dyDescent="0.25">
@@ -7952,15 +7934,15 @@
         <v>0.1351</v>
       </c>
       <c r="E170" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H170" s="6"/>
       <c r="I170" s="6"/>
       <c r="J170" s="6" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="K170" s="6" t="s">
-        <v>916</v>
+        <v>910</v>
       </c>
     </row>
     <row r="171" spans="1:11" x14ac:dyDescent="0.25">
@@ -7977,15 +7959,15 @@
         <v>0.1351</v>
       </c>
       <c r="E171" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H171" s="6"/>
       <c r="I171" s="6"/>
       <c r="J171" s="6" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="K171" s="6" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
     </row>
     <row r="172" spans="1:11" x14ac:dyDescent="0.25">
@@ -8002,15 +7984,15 @@
         <v>0.1351</v>
       </c>
       <c r="E172" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H172" s="6"/>
       <c r="I172" s="6"/>
       <c r="J172" s="6" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="K172" s="6" t="s">
-        <v>918</v>
+        <v>912</v>
       </c>
     </row>
     <row r="173" spans="1:11" x14ac:dyDescent="0.25">
@@ -8027,15 +8009,15 @@
         <v>0.1351</v>
       </c>
       <c r="E173" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H173" s="6"/>
       <c r="I173" s="6"/>
       <c r="J173" s="6" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="K173" s="6" t="s">
-        <v>919</v>
+        <v>913</v>
       </c>
     </row>
     <row r="174" spans="1:11" x14ac:dyDescent="0.25">
@@ -8052,15 +8034,15 @@
         <v>3.5200000000000002E-2</v>
       </c>
       <c r="E174" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H174" s="6"/>
       <c r="I174" s="6"/>
       <c r="J174" s="6" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="K174" s="6" t="s">
-        <v>920</v>
+        <v>914</v>
       </c>
     </row>
     <row r="175" spans="1:11" x14ac:dyDescent="0.25">
@@ -8077,15 +8059,15 @@
         <v>3.5200000000000002E-2</v>
       </c>
       <c r="E175" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H175" s="6"/>
       <c r="I175" s="6"/>
       <c r="J175" s="6" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="K175" s="6" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
     </row>
     <row r="176" spans="1:11" x14ac:dyDescent="0.25">
@@ -8102,15 +8084,15 @@
         <v>3.5200000000000002E-2</v>
       </c>
       <c r="E176" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H176" s="6"/>
       <c r="I176" s="6"/>
       <c r="J176" s="6" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="K176" s="6" t="s">
-        <v>922</v>
+        <v>916</v>
       </c>
     </row>
     <row r="177" spans="1:13" x14ac:dyDescent="0.25">
@@ -8127,15 +8109,15 @@
         <v>3.5200000000000002E-2</v>
       </c>
       <c r="E177" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H177" s="6"/>
       <c r="I177" s="6"/>
       <c r="J177" s="6" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="K177" s="6" t="s">
-        <v>923</v>
+        <v>917</v>
       </c>
     </row>
     <row r="178" spans="1:13" x14ac:dyDescent="0.25">
@@ -8152,15 +8134,15 @@
         <v>9.7199999999999995E-2</v>
       </c>
       <c r="E178" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H178" s="6"/>
       <c r="I178" s="6"/>
       <c r="J178" s="6" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="K178" s="6" t="s">
-        <v>924</v>
+        <v>918</v>
       </c>
     </row>
     <row r="179" spans="1:13" x14ac:dyDescent="0.25">
@@ -8177,15 +8159,15 @@
         <v>9.7199999999999995E-2</v>
       </c>
       <c r="E179" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H179" s="6"/>
       <c r="I179" s="6"/>
       <c r="J179" s="6" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="K179" s="6" t="s">
-        <v>925</v>
+        <v>919</v>
       </c>
     </row>
     <row r="180" spans="1:13" x14ac:dyDescent="0.25">
@@ -8202,7 +8184,7 @@
         <v>1.54E-2</v>
       </c>
       <c r="E180" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H180" s="6"/>
       <c r="I180" s="6"/>
@@ -8226,7 +8208,7 @@
         <v>7.5499999999999998E-2</v>
       </c>
       <c r="E181" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H181" s="6"/>
       <c r="I181" s="6"/>
@@ -8250,10 +8232,10 @@
         <v>0.17549999999999999</v>
       </c>
       <c r="E182" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="F182" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G182">
         <v>3</v>
@@ -8261,10 +8243,10 @@
       <c r="H182" s="6"/>
       <c r="I182" s="6"/>
       <c r="J182" s="6" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="K182" s="6" t="s">
-        <v>926</v>
+        <v>920</v>
       </c>
     </row>
     <row r="183" spans="1:13" x14ac:dyDescent="0.25">
@@ -8281,15 +8263,15 @@
         <v>0.17549999999999999</v>
       </c>
       <c r="E183" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H183" s="6"/>
       <c r="I183" s="6"/>
       <c r="J183" s="6" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="K183" s="6" t="s">
-        <v>927</v>
+        <v>921</v>
       </c>
     </row>
     <row r="184" spans="1:13" x14ac:dyDescent="0.25">
@@ -8306,15 +8288,15 @@
         <v>0.17549999999999999</v>
       </c>
       <c r="E184" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H184" s="6"/>
       <c r="I184" s="6"/>
       <c r="J184" s="6" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="K184" s="6" t="s">
-        <v>928</v>
+        <v>922</v>
       </c>
     </row>
     <row r="185" spans="1:13" x14ac:dyDescent="0.25">
@@ -8331,10 +8313,10 @@
         <v>0.1013</v>
       </c>
       <c r="E185" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="F185" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G185">
         <v>3</v>
@@ -8342,10 +8324,10 @@
       <c r="H185" s="6"/>
       <c r="I185" s="6"/>
       <c r="J185" s="6" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="K185" s="6" t="s">
-        <v>929</v>
+        <v>923</v>
       </c>
     </row>
     <row r="186" spans="1:13" x14ac:dyDescent="0.25">
@@ -8362,15 +8344,15 @@
         <v>0.1013</v>
       </c>
       <c r="E186" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H186" s="6"/>
       <c r="I186" s="6"/>
       <c r="J186" s="6" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="K186" s="6" t="s">
-        <v>930</v>
+        <v>924</v>
       </c>
     </row>
     <row r="187" spans="1:13" x14ac:dyDescent="0.25">
@@ -8387,15 +8369,15 @@
         <v>0.1013</v>
       </c>
       <c r="E187" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H187" s="6"/>
       <c r="I187" s="6"/>
       <c r="J187" s="6" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="K187" s="6" t="s">
-        <v>931</v>
+        <v>925</v>
       </c>
     </row>
     <row r="188" spans="1:13" x14ac:dyDescent="0.25">
@@ -8412,15 +8394,15 @@
         <v>0.1013</v>
       </c>
       <c r="E188" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H188" s="6"/>
       <c r="I188" s="6"/>
       <c r="J188" s="6" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="K188" s="6" t="s">
-        <v>932</v>
+        <v>926</v>
       </c>
     </row>
     <row r="189" spans="1:13" x14ac:dyDescent="0.25">
@@ -8437,15 +8419,15 @@
         <v>8.7999999999999995E-2</v>
       </c>
       <c r="E189" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H189" s="6"/>
       <c r="I189" s="6"/>
       <c r="J189" s="6" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="K189" s="6" t="s">
-        <v>933</v>
+        <v>927</v>
       </c>
     </row>
     <row r="190" spans="1:13" x14ac:dyDescent="0.25">
@@ -8462,15 +8444,15 @@
         <v>8.7999999999999995E-2</v>
       </c>
       <c r="E190" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H190" s="6"/>
       <c r="I190" s="6"/>
       <c r="J190" s="6" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="K190" s="6" t="s">
-        <v>934</v>
+        <v>928</v>
       </c>
     </row>
     <row r="191" spans="1:13" x14ac:dyDescent="0.25">
@@ -8487,7 +8469,7 @@
         <v>6.7637999999999998</v>
       </c>
       <c r="E191" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="H191" s="6"/>
       <c r="I191" s="6"/>
@@ -8511,15 +8493,15 @@
         <v>6.9599999999999995E-2</v>
       </c>
       <c r="E192" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="H192" s="6"/>
       <c r="I192" s="6"/>
       <c r="J192" s="6" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="K192" s="6" t="s">
-        <v>935</v>
+        <v>929</v>
       </c>
     </row>
     <row r="193" spans="1:13" x14ac:dyDescent="0.25">
@@ -8536,15 +8518,15 @@
         <v>6.9599999999999995E-2</v>
       </c>
       <c r="E193" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="H193" s="6"/>
       <c r="I193" s="6"/>
       <c r="J193" s="6" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="K193" s="6" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
     </row>
     <row r="194" spans="1:13" x14ac:dyDescent="0.25">
@@ -8561,15 +8543,15 @@
         <v>6.9599999999999995E-2</v>
       </c>
       <c r="E194" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="H194" s="6"/>
       <c r="I194" s="6"/>
       <c r="J194" s="6" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="K194" s="6" t="s">
-        <v>937</v>
+        <v>931</v>
       </c>
     </row>
     <row r="195" spans="1:13" x14ac:dyDescent="0.25">
@@ -8586,15 +8568,15 @@
         <v>6.9599999999999995E-2</v>
       </c>
       <c r="E195" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="H195" s="6"/>
       <c r="I195" s="6"/>
       <c r="J195" s="6" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="K195" s="6" t="s">
-        <v>938</v>
+        <v>932</v>
       </c>
     </row>
     <row r="196" spans="1:13" x14ac:dyDescent="0.25">
@@ -8611,15 +8593,15 @@
         <v>6.9599999999999995E-2</v>
       </c>
       <c r="E196" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="H196" s="6"/>
       <c r="I196" s="6"/>
       <c r="J196" s="6" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="K196" s="6" t="s">
-        <v>939</v>
+        <v>933</v>
       </c>
     </row>
     <row r="197" spans="1:13" x14ac:dyDescent="0.25">
@@ -8636,7 +8618,7 @@
         <v>0.44969999999999999</v>
       </c>
       <c r="E197" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="H197" s="6"/>
       <c r="I197" s="6"/>
@@ -8660,7 +8642,7 @@
         <v>0.66210000000000002</v>
       </c>
       <c r="E198" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="H198" s="6"/>
       <c r="I198" s="6"/>
@@ -8684,10 +8666,10 @@
         <v>1.2737000000000001</v>
       </c>
       <c r="E199" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="F199" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G199">
         <v>4</v>
@@ -8714,10 +8696,10 @@
         <v>0.54090000000000005</v>
       </c>
       <c r="E200" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="F200" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G200">
         <v>4</v>
@@ -8744,7 +8726,7 @@
         <v>0.54090000000000005</v>
       </c>
       <c r="E201" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="H201" s="6"/>
       <c r="I201" s="6"/>
@@ -8768,10 +8750,10 @@
         <v>0.32269999999999999</v>
       </c>
       <c r="E202" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="F202" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G202">
         <v>4</v>
@@ -8779,10 +8761,10 @@
       <c r="H202" s="6"/>
       <c r="I202" s="6"/>
       <c r="J202" s="6" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="K202" s="6" t="s">
-        <v>940</v>
+        <v>934</v>
       </c>
     </row>
     <row r="203" spans="1:13" x14ac:dyDescent="0.25">
@@ -8799,15 +8781,15 @@
         <v>0.34549999999999997</v>
       </c>
       <c r="E203" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="H203" s="6"/>
       <c r="I203" s="6"/>
       <c r="J203" s="6" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="K203" s="6" t="s">
-        <v>942</v>
+        <v>936</v>
       </c>
     </row>
     <row r="204" spans="1:13" x14ac:dyDescent="0.25">
@@ -8824,15 +8806,15 @@
         <v>0.1545</v>
       </c>
       <c r="E204" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="H204" s="6"/>
       <c r="I204" s="6"/>
       <c r="J204" s="6" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="K204" s="6" t="s">
-        <v>941</v>
+        <v>935</v>
       </c>
     </row>
     <row r="205" spans="1:13" x14ac:dyDescent="0.25">
@@ -8849,15 +8831,15 @@
         <v>0.32790000000000002</v>
       </c>
       <c r="E205" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H205" s="6"/>
       <c r="I205" s="6"/>
       <c r="J205" s="6" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="K205" s="6" t="s">
-        <v>943</v>
+        <v>937</v>
       </c>
     </row>
     <row r="206" spans="1:13" x14ac:dyDescent="0.25">
@@ -8874,15 +8856,15 @@
         <v>0.32790000000000002</v>
       </c>
       <c r="E206" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H206" s="6"/>
       <c r="I206" s="6"/>
       <c r="J206" s="6" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="K206" s="6" t="s">
-        <v>944</v>
+        <v>938</v>
       </c>
     </row>
     <row r="207" spans="1:13" x14ac:dyDescent="0.25">
@@ -8899,15 +8881,15 @@
         <v>0.32790000000000002</v>
       </c>
       <c r="E207" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H207" s="6"/>
       <c r="I207" s="6"/>
       <c r="J207" s="6" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="K207" s="6" t="s">
-        <v>945</v>
+        <v>939</v>
       </c>
     </row>
     <row r="208" spans="1:13" x14ac:dyDescent="0.25">
@@ -8924,15 +8906,15 @@
         <v>0.32790000000000002</v>
       </c>
       <c r="E208" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H208" s="6"/>
       <c r="I208" s="6"/>
       <c r="J208" s="6" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="K208" s="6" t="s">
-        <v>946</v>
+        <v>940</v>
       </c>
     </row>
     <row r="209" spans="1:11" x14ac:dyDescent="0.25">
@@ -8949,15 +8931,15 @@
         <v>0.32790000000000002</v>
       </c>
       <c r="E209" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H209" s="6"/>
       <c r="I209" s="6"/>
       <c r="J209" s="6" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="K209" s="6" t="s">
-        <v>947</v>
+        <v>941</v>
       </c>
     </row>
     <row r="210" spans="1:11" x14ac:dyDescent="0.25">
@@ -8974,15 +8956,15 @@
         <v>0.32790000000000002</v>
       </c>
       <c r="E210" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H210" s="6"/>
       <c r="I210" s="6"/>
       <c r="J210" s="6" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="K210" s="6" t="s">
-        <v>948</v>
+        <v>942</v>
       </c>
     </row>
     <row r="211" spans="1:11" x14ac:dyDescent="0.25">
@@ -8999,15 +8981,15 @@
         <v>0.32790000000000002</v>
       </c>
       <c r="E211" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H211" s="6"/>
       <c r="I211" s="6"/>
       <c r="J211" s="6" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="K211" s="6" t="s">
-        <v>949</v>
+        <v>943</v>
       </c>
     </row>
     <row r="212" spans="1:11" x14ac:dyDescent="0.25">
@@ -9024,15 +9006,15 @@
         <v>0.32790000000000002</v>
       </c>
       <c r="E212" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H212" s="6"/>
       <c r="I212" s="6"/>
       <c r="J212" s="6" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="K212" s="6" t="s">
-        <v>950</v>
+        <v>944</v>
       </c>
     </row>
     <row r="213" spans="1:11" x14ac:dyDescent="0.25">
@@ -9049,15 +9031,15 @@
         <v>0.37259999999999999</v>
       </c>
       <c r="E213" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H213" s="6"/>
       <c r="I213" s="6"/>
       <c r="J213" s="6" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="K213" s="6" t="s">
-        <v>951</v>
+        <v>945</v>
       </c>
     </row>
     <row r="214" spans="1:11" x14ac:dyDescent="0.25">
@@ -9074,15 +9056,15 @@
         <v>7.6999999999999999E-2</v>
       </c>
       <c r="E214" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H214" s="6"/>
       <c r="I214" s="6"/>
       <c r="J214" s="6" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="K214" s="6" t="s">
-        <v>952</v>
+        <v>946</v>
       </c>
     </row>
     <row r="215" spans="1:11" x14ac:dyDescent="0.25">
@@ -9099,15 +9081,15 @@
         <v>7.6999999999999999E-2</v>
       </c>
       <c r="E215" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H215" s="6"/>
       <c r="I215" s="6"/>
       <c r="J215" s="6" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="K215" s="6" t="s">
-        <v>953</v>
+        <v>947</v>
       </c>
     </row>
     <row r="216" spans="1:11" x14ac:dyDescent="0.25">
@@ -9124,15 +9106,15 @@
         <v>7.6999999999999999E-2</v>
       </c>
       <c r="E216" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H216" s="6"/>
       <c r="I216" s="6"/>
       <c r="J216" s="6" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="K216" s="6" t="s">
-        <v>954</v>
+        <v>948</v>
       </c>
     </row>
     <row r="217" spans="1:11" x14ac:dyDescent="0.25">
@@ -9149,15 +9131,15 @@
         <v>4.7300000000000002E-2</v>
       </c>
       <c r="E217" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H217" s="6"/>
       <c r="I217" s="6"/>
       <c r="J217" s="6" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="K217" s="6" t="s">
-        <v>955</v>
+        <v>949</v>
       </c>
     </row>
     <row r="218" spans="1:11" x14ac:dyDescent="0.25">
@@ -9174,15 +9156,15 @@
         <v>4.7300000000000002E-2</v>
       </c>
       <c r="E218" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H218" s="6"/>
       <c r="I218" s="6"/>
       <c r="J218" s="6" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="K218" s="6" t="s">
-        <v>956</v>
+        <v>950</v>
       </c>
     </row>
     <row r="219" spans="1:11" x14ac:dyDescent="0.25">
@@ -9199,15 +9181,15 @@
         <v>4.7300000000000002E-2</v>
       </c>
       <c r="E219" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H219" s="6"/>
       <c r="I219" s="6"/>
       <c r="J219" s="6" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="K219" s="6" t="s">
-        <v>957</v>
+        <v>951</v>
       </c>
     </row>
     <row r="220" spans="1:11" x14ac:dyDescent="0.25">
@@ -9224,15 +9206,15 @@
         <v>4.7300000000000002E-2</v>
       </c>
       <c r="E220" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H220" s="6"/>
       <c r="I220" s="6"/>
       <c r="J220" s="6" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="K220" s="6" t="s">
-        <v>958</v>
+        <v>952</v>
       </c>
     </row>
     <row r="221" spans="1:11" x14ac:dyDescent="0.25">
@@ -9249,15 +9231,15 @@
         <v>4.7300000000000002E-2</v>
       </c>
       <c r="E221" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H221" s="6"/>
       <c r="I221" s="6"/>
       <c r="J221" s="6" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K221" s="6" t="s">
-        <v>959</v>
+        <v>953</v>
       </c>
     </row>
     <row r="222" spans="1:11" x14ac:dyDescent="0.25">
@@ -9274,15 +9256,15 @@
         <v>4.7300000000000002E-2</v>
       </c>
       <c r="E222" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H222" s="6"/>
       <c r="I222" s="6"/>
       <c r="J222" s="6" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="K222" s="6" t="s">
-        <v>960</v>
+        <v>954</v>
       </c>
     </row>
     <row r="223" spans="1:11" x14ac:dyDescent="0.25">
@@ -9299,15 +9281,15 @@
         <v>5.3900000000000003E-2</v>
       </c>
       <c r="E223" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H223" s="6"/>
       <c r="I223" s="6"/>
       <c r="J223" s="6" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="K223" s="6" t="s">
-        <v>961</v>
+        <v>955</v>
       </c>
     </row>
     <row r="224" spans="1:11" x14ac:dyDescent="0.25">
@@ -9324,15 +9306,15 @@
         <v>5.8000000000000003E-2</v>
       </c>
       <c r="E224" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H224" s="6"/>
       <c r="I224" s="6"/>
       <c r="J224" s="6" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="K224" s="6" t="s">
-        <v>962</v>
+        <v>956</v>
       </c>
     </row>
     <row r="225" spans="1:13" x14ac:dyDescent="0.25">
@@ -9349,15 +9331,15 @@
         <v>5.8000000000000003E-2</v>
       </c>
       <c r="E225" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H225" s="6"/>
       <c r="I225" s="6"/>
       <c r="J225" s="6" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="K225" s="6" t="s">
-        <v>963</v>
+        <v>957</v>
       </c>
     </row>
     <row r="226" spans="1:13" x14ac:dyDescent="0.25">
@@ -9374,10 +9356,10 @@
         <v>0.1699</v>
       </c>
       <c r="E226" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="F226" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G226">
         <v>5</v>
@@ -9385,10 +9367,10 @@
       <c r="H226" s="6"/>
       <c r="I226" s="6"/>
       <c r="J226" s="6" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="K226" s="6" t="s">
-        <v>964</v>
+        <v>958</v>
       </c>
     </row>
     <row r="227" spans="1:13" x14ac:dyDescent="0.25">
@@ -9405,15 +9387,15 @@
         <v>0.1699</v>
       </c>
       <c r="E227" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H227" s="6"/>
       <c r="I227" s="6"/>
       <c r="J227" s="6" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="K227" s="6" t="s">
-        <v>965</v>
+        <v>959</v>
       </c>
     </row>
     <row r="228" spans="1:13" x14ac:dyDescent="0.25">
@@ -9430,15 +9412,15 @@
         <v>0.1699</v>
       </c>
       <c r="E228" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H228" s="6"/>
       <c r="I228" s="6"/>
       <c r="J228" s="6" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="K228" s="6" t="s">
-        <v>966</v>
+        <v>960</v>
       </c>
     </row>
     <row r="229" spans="1:13" x14ac:dyDescent="0.25">
@@ -9455,15 +9437,15 @@
         <v>0.1699</v>
       </c>
       <c r="E229" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H229" s="6"/>
       <c r="I229" s="6"/>
       <c r="J229" s="6" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="K229" s="6" t="s">
-        <v>967</v>
+        <v>961</v>
       </c>
     </row>
     <row r="230" spans="1:13" x14ac:dyDescent="0.25">
@@ -9480,10 +9462,10 @@
         <v>0.18959999999999999</v>
       </c>
       <c r="E230" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="F230" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G230">
         <v>5</v>
@@ -9491,10 +9473,10 @@
       <c r="H230" s="6"/>
       <c r="I230" s="6"/>
       <c r="J230" s="6" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="K230" s="6" t="s">
-        <v>968</v>
+        <v>962</v>
       </c>
     </row>
     <row r="231" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -9511,15 +9493,15 @@
         <v>0.18959999999999999</v>
       </c>
       <c r="E231" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H231" s="6"/>
       <c r="I231" s="6"/>
       <c r="J231" s="6" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="K231" s="6" t="s">
-        <v>969</v>
+        <v>963</v>
       </c>
     </row>
     <row r="232" spans="1:13" x14ac:dyDescent="0.25">
@@ -9536,15 +9518,15 @@
         <v>0.1062</v>
       </c>
       <c r="E232" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H232" s="6"/>
       <c r="I232" s="6"/>
       <c r="J232" s="6" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="K232" s="6" t="s">
-        <v>970</v>
+        <v>964</v>
       </c>
     </row>
     <row r="233" spans="1:13" x14ac:dyDescent="0.25">
@@ -9561,15 +9543,15 @@
         <v>0.1062</v>
       </c>
       <c r="E233" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H233" s="6"/>
       <c r="I233" s="6"/>
       <c r="J233" s="6" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="K233" s="6" t="s">
-        <v>971</v>
+        <v>965</v>
       </c>
     </row>
     <row r="234" spans="1:13" x14ac:dyDescent="0.25">
@@ -9586,10 +9568,10 @@
         <v>0.22020000000000001</v>
       </c>
       <c r="E234" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="F234" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G234">
         <v>5</v>
@@ -9597,10 +9579,10 @@
       <c r="H234" s="6"/>
       <c r="I234" s="6"/>
       <c r="J234" s="6" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="K234" s="6" t="s">
-        <v>972</v>
+        <v>966</v>
       </c>
     </row>
     <row r="235" spans="1:13" x14ac:dyDescent="0.25">
@@ -9617,15 +9599,15 @@
         <v>4.3700000000000003E-2</v>
       </c>
       <c r="E235" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H235" s="6"/>
       <c r="I235" s="6"/>
       <c r="J235" s="6" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="K235" s="6" t="s">
-        <v>973</v>
+        <v>967</v>
       </c>
     </row>
     <row r="236" spans="1:13" x14ac:dyDescent="0.25">
@@ -9642,15 +9624,15 @@
         <v>4.3700000000000003E-2</v>
       </c>
       <c r="E236" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H236" s="6"/>
       <c r="I236" s="6"/>
       <c r="J236" s="6" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="K236" s="6" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
     </row>
     <row r="237" spans="1:13" x14ac:dyDescent="0.25">
@@ -9667,15 +9649,15 @@
         <v>5.0200000000000002E-2</v>
       </c>
       <c r="E237" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H237" s="6"/>
       <c r="I237" s="6"/>
       <c r="J237" s="6" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="K237" s="6" t="s">
-        <v>975</v>
+        <v>969</v>
       </c>
     </row>
     <row r="238" spans="1:13" x14ac:dyDescent="0.25">
@@ -9692,15 +9674,15 @@
         <v>5.3400000000000003E-2</v>
       </c>
       <c r="E238" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H238" s="6"/>
       <c r="I238" s="6"/>
       <c r="J238" s="6" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="K238" s="6" t="s">
-        <v>976</v>
+        <v>970</v>
       </c>
     </row>
     <row r="239" spans="1:13" x14ac:dyDescent="0.25">
@@ -9717,10 +9699,10 @@
         <v>0.1525</v>
       </c>
       <c r="E239" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="F239" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G239">
         <v>5</v>
@@ -9747,15 +9729,15 @@
         <v>0.16189999999999999</v>
       </c>
       <c r="E240" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H240" s="6"/>
       <c r="I240" s="6"/>
       <c r="J240" s="6" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="K240" s="6" t="s">
-        <v>977</v>
+        <v>971</v>
       </c>
     </row>
     <row r="241" spans="1:13" x14ac:dyDescent="0.25">
@@ -9772,15 +9754,15 @@
         <v>0.16189999999999999</v>
       </c>
       <c r="E241" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H241" s="6"/>
       <c r="I241" s="6"/>
       <c r="J241" s="6" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="K241" s="6" t="s">
-        <v>978</v>
+        <v>972</v>
       </c>
     </row>
     <row r="242" spans="1:13" x14ac:dyDescent="0.25">
@@ -9797,10 +9779,10 @@
         <v>5.8599999999999999E-2</v>
       </c>
       <c r="E242" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="F242" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G242">
         <v>5</v>
@@ -9808,10 +9790,10 @@
       <c r="H242" s="6"/>
       <c r="I242" s="6"/>
       <c r="J242" s="6" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="K242" s="6" t="s">
-        <v>979</v>
+        <v>973</v>
       </c>
     </row>
     <row r="243" spans="1:13" x14ac:dyDescent="0.25">
@@ -9828,10 +9810,10 @@
         <v>0.1326</v>
       </c>
       <c r="E243" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="F243" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G243">
         <v>5</v>
@@ -9839,10 +9821,10 @@
       <c r="H243" s="6"/>
       <c r="I243" s="6"/>
       <c r="J243" s="6" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="K243" s="6" t="s">
-        <v>980</v>
+        <v>974</v>
       </c>
     </row>
     <row r="244" spans="1:13" x14ac:dyDescent="0.25">
@@ -9859,15 +9841,15 @@
         <v>0.1326</v>
       </c>
       <c r="E244" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H244" s="6"/>
       <c r="I244" s="6"/>
       <c r="J244" s="6" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="K244" s="6" t="s">
-        <v>981</v>
+        <v>975</v>
       </c>
     </row>
     <row r="245" spans="1:13" x14ac:dyDescent="0.25">
@@ -9884,15 +9866,15 @@
         <v>0.1326</v>
       </c>
       <c r="E245" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H245" s="6"/>
       <c r="I245" s="6"/>
       <c r="J245" s="6" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="K245" s="6" t="s">
-        <v>982</v>
+        <v>976</v>
       </c>
     </row>
     <row r="246" spans="1:13" x14ac:dyDescent="0.25">
@@ -9909,10 +9891,10 @@
         <v>8.8499999999999995E-2</v>
       </c>
       <c r="E246" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="F246" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G246">
         <v>5</v>
@@ -9920,10 +9902,10 @@
       <c r="H246" s="6"/>
       <c r="I246" s="6"/>
       <c r="J246" s="6" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="K246" s="6" t="s">
-        <v>983</v>
+        <v>977</v>
       </c>
     </row>
     <row r="247" spans="1:13" x14ac:dyDescent="0.25">
@@ -9940,15 +9922,15 @@
         <v>8.8499999999999995E-2</v>
       </c>
       <c r="E247" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H247" s="6"/>
       <c r="I247" s="6"/>
       <c r="J247" s="6" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="K247" s="6" t="s">
-        <v>984</v>
+        <v>978</v>
       </c>
     </row>
     <row r="248" spans="1:13" x14ac:dyDescent="0.25">
@@ -9965,19 +9947,19 @@
         <v>0.16800000000000001</v>
       </c>
       <c r="E248" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="F248" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G248">
         <v>5</v>
       </c>
       <c r="H248" s="6" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="I248" s="6" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
       <c r="J248" s="6"/>
       <c r="K248" s="6"/>
@@ -9996,19 +9978,19 @@
         <v>0.16800000000000001</v>
       </c>
       <c r="E249" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="F249" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G249">
         <v>5</v>
       </c>
       <c r="H249" s="6" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="I249" s="6" t="s">
-        <v>857</v>
+        <v>853</v>
       </c>
       <c r="J249" s="6"/>
       <c r="K249" s="6"/>
@@ -10027,13 +10009,13 @@
         <v>0.16800000000000001</v>
       </c>
       <c r="E250" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H250" s="6" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="I250" s="6" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
       <c r="J250" s="6"/>
       <c r="K250" s="6"/>
@@ -10052,13 +10034,13 @@
         <v>0.16800000000000001</v>
       </c>
       <c r="E251" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H251" s="6" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="I251" s="6" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="J251" s="6"/>
       <c r="K251" s="6"/>
@@ -10077,13 +10059,13 @@
         <v>0.16800000000000001</v>
       </c>
       <c r="E252" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H252" s="6" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="I252" s="6" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="J252" s="6"/>
       <c r="K252" s="6"/>
@@ -10102,13 +10084,13 @@
         <v>6.6199999999999995E-2</v>
       </c>
       <c r="E253" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H253" s="6" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="I253" s="6" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
       <c r="J253" s="6"/>
       <c r="K253" s="6"/>
@@ -10127,13 +10109,13 @@
         <v>6.6199999999999995E-2</v>
       </c>
       <c r="E254" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H254" s="6" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="I254" s="6" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="J254" s="6"/>
       <c r="K254" s="6"/>
@@ -10152,7 +10134,7 @@
         <v>6.6199999999999995E-2</v>
       </c>
       <c r="E255" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H255" s="6"/>
       <c r="I255" s="6"/>
@@ -10173,7 +10155,7 @@
         <v>0.15040000000000001</v>
       </c>
       <c r="E256" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H256" s="6"/>
       <c r="I256" s="6"/>
@@ -10197,7 +10179,7 @@
         <v>0.15040000000000001</v>
       </c>
       <c r="E257" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H257" s="6"/>
       <c r="I257" s="6"/>
@@ -10221,7 +10203,7 @@
         <v>0.34360000000000002</v>
       </c>
       <c r="E258" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="H258" s="6"/>
       <c r="I258" s="6"/>
@@ -10245,7 +10227,7 @@
         <v>0.34360000000000002</v>
       </c>
       <c r="E259" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="H259" s="6"/>
       <c r="I259" s="6"/>
@@ -10269,10 +10251,10 @@
         <v>0.1116</v>
       </c>
       <c r="E260" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="F260" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G260">
         <v>6</v>
@@ -10280,10 +10262,10 @@
       <c r="H260" s="6"/>
       <c r="I260" s="6"/>
       <c r="J260" s="6" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="K260" s="6" t="s">
-        <v>985</v>
+        <v>979</v>
       </c>
     </row>
     <row r="261" spans="1:13" x14ac:dyDescent="0.25">
@@ -10300,15 +10282,15 @@
         <v>0.1116</v>
       </c>
       <c r="E261" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="H261" s="6"/>
       <c r="I261" s="6"/>
       <c r="J261" s="6" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="K261" s="6" t="s">
-        <v>986</v>
+        <v>980</v>
       </c>
     </row>
     <row r="262" spans="1:13" x14ac:dyDescent="0.25">
@@ -10325,7 +10307,7 @@
         <v>9.3200000000000005E-2</v>
       </c>
       <c r="E262" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="H262" s="6"/>
       <c r="I262" s="6"/>
@@ -10346,7 +10328,7 @@
         <v>0.14940000000000001</v>
       </c>
       <c r="E263" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="H263" s="6"/>
       <c r="I263" s="6"/>
@@ -10370,7 +10352,7 @@
         <v>0.14940000000000001</v>
       </c>
       <c r="E264" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="H264" s="6"/>
       <c r="I264" s="6"/>
@@ -10394,7 +10376,7 @@
         <v>0.14940000000000001</v>
       </c>
       <c r="E265" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="H265" s="6"/>
       <c r="I265" s="6"/>
@@ -10418,7 +10400,7 @@
         <v>0.14940000000000001</v>
       </c>
       <c r="E266" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="H266" s="6"/>
       <c r="I266" s="6"/>
@@ -10442,10 +10424,10 @@
         <v>0.13289999999999999</v>
       </c>
       <c r="E267" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="F267" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G267">
         <v>6</v>
@@ -10472,7 +10454,7 @@
         <v>0.13289999999999999</v>
       </c>
       <c r="E268" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="H268" s="6"/>
       <c r="I268" s="6"/>
@@ -10496,7 +10478,7 @@
         <v>0.13289999999999999</v>
       </c>
       <c r="E269" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="H269" s="6"/>
       <c r="I269" s="6"/>
@@ -10520,7 +10502,7 @@
         <v>0.2407</v>
       </c>
       <c r="E270" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="H270" s="6"/>
       <c r="I270" s="6"/>
@@ -10544,7 +10526,7 @@
         <v>0.2407</v>
       </c>
       <c r="E271" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="H271" s="6"/>
       <c r="I271" s="6"/>
@@ -10568,7 +10550,7 @@
         <v>0.2407</v>
       </c>
       <c r="E272" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="H272" s="6"/>
       <c r="I272" s="6"/>
@@ -10592,7 +10574,7 @@
         <v>1.7399999999999999E-2</v>
       </c>
       <c r="E273" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="H273" s="6"/>
       <c r="I273" s="6"/>
@@ -10616,7 +10598,7 @@
         <v>1.7399999999999999E-2</v>
       </c>
       <c r="E274" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="H274" s="6"/>
       <c r="I274" s="6"/>
@@ -10640,7 +10622,7 @@
         <v>1.7399999999999999E-2</v>
       </c>
       <c r="E275" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="H275" s="6"/>
       <c r="I275" s="6"/>
@@ -10664,7 +10646,7 @@
         <v>1.7399999999999999E-2</v>
       </c>
       <c r="E276" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="H276" s="6"/>
       <c r="I276" s="6"/>
@@ -10688,10 +10670,10 @@
         <v>1.5285</v>
       </c>
       <c r="E277" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="F277" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G277">
         <v>7</v>
@@ -10718,7 +10700,7 @@
         <v>1.5285</v>
       </c>
       <c r="E278" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="H278" s="6"/>
       <c r="I278" s="6"/>
@@ -10742,7 +10724,7 @@
         <v>1.5285</v>
       </c>
       <c r="E279" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="H279" s="6"/>
       <c r="I279" s="6"/>
@@ -10766,7 +10748,7 @@
         <v>1.5285</v>
       </c>
       <c r="E280" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="H280" s="6"/>
       <c r="I280" s="6"/>
@@ -10790,10 +10772,10 @@
         <v>0.47689999999999999</v>
       </c>
       <c r="E281" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="F281" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G281">
         <v>7</v>
@@ -10820,10 +10802,10 @@
         <v>5.5300000000000002E-2</v>
       </c>
       <c r="E282" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="F282" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G282">
         <v>7</v>
@@ -10831,10 +10813,10 @@
       <c r="H282" s="6"/>
       <c r="I282" s="6"/>
       <c r="J282" s="6" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="K282" s="6" t="s">
-        <v>987</v>
+        <v>981</v>
       </c>
     </row>
     <row r="283" spans="1:13" x14ac:dyDescent="0.25">
@@ -10851,15 +10833,15 @@
         <v>0.18360000000000001</v>
       </c>
       <c r="E283" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="H283" s="6"/>
       <c r="I283" s="6"/>
       <c r="J283" s="6" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="K283" s="6" t="s">
-        <v>988</v>
+        <v>982</v>
       </c>
     </row>
     <row r="284" spans="1:13" x14ac:dyDescent="0.25">
@@ -10876,15 +10858,15 @@
         <v>0.1124</v>
       </c>
       <c r="E284" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="H284" s="6"/>
       <c r="I284" s="6"/>
       <c r="J284" s="6" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="K284" s="6" t="s">
-        <v>989</v>
+        <v>983</v>
       </c>
     </row>
     <row r="285" spans="1:13" x14ac:dyDescent="0.25">
@@ -10901,15 +10883,15 @@
         <v>6.2399999999999997E-2</v>
       </c>
       <c r="E285" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="H285" s="6"/>
       <c r="I285" s="6"/>
       <c r="J285" s="6" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="K285" s="6" t="s">
-        <v>990</v>
+        <v>984</v>
       </c>
     </row>
     <row r="286" spans="1:13" x14ac:dyDescent="0.25">
@@ -10926,7 +10908,7 @@
         <v>1.3918999999999999</v>
       </c>
       <c r="E286" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="H286" s="6"/>
       <c r="I286" s="6"/>
@@ -10950,7 +10932,7 @@
         <v>1.2363999999999999</v>
       </c>
       <c r="E287" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="H287" s="6"/>
       <c r="I287" s="6"/>
@@ -10974,7 +10956,7 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="E288" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="H288" s="6"/>
       <c r="I288" s="6"/>
@@ -10998,7 +10980,7 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="E289" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="H289" s="6"/>
       <c r="I289" s="6"/>
@@ -11022,15 +11004,15 @@
         <v>2.07E-2</v>
       </c>
       <c r="E290" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="H290" s="6"/>
       <c r="I290" s="6"/>
       <c r="J290" s="6" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="K290" s="6" t="s">
-        <v>991</v>
+        <v>985</v>
       </c>
     </row>
     <row r="291" spans="1:13" x14ac:dyDescent="0.25">
@@ -11047,10 +11029,10 @@
         <v>0.49580000000000002</v>
       </c>
       <c r="E291" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="F291" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G291">
         <v>7</v>
@@ -11077,7 +11059,7 @@
         <v>0.49580000000000002</v>
       </c>
       <c r="E292" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="H292" s="6"/>
       <c r="I292" s="6"/>
@@ -11101,7 +11083,7 @@
         <v>1.7100000000000001E-2</v>
       </c>
       <c r="E293" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="H293" s="6"/>
       <c r="I293" s="6"/>
@@ -11125,7 +11107,7 @@
         <v>1.7100000000000001E-2</v>
       </c>
       <c r="E294" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="H294" s="6"/>
       <c r="I294" s="6"/>
@@ -11149,7 +11131,7 @@
         <v>9.5000000000000001E-2</v>
       </c>
       <c r="E295" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="H295" s="6"/>
       <c r="I295" s="6"/>
@@ -11173,7 +11155,7 @@
         <v>9.5000000000000001E-2</v>
       </c>
       <c r="E296" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="H296" s="6"/>
       <c r="I296" s="6"/>
@@ -11197,7 +11179,7 @@
         <v>7.2300000000000003E-2</v>
       </c>
       <c r="E297" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="H297" s="6"/>
       <c r="I297" s="6"/>
@@ -11221,10 +11203,10 @@
         <v>9.8400000000000001E-2</v>
       </c>
       <c r="E298" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="F298" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G298">
         <v>7</v>
@@ -11251,7 +11233,7 @@
         <v>9.8400000000000001E-2</v>
       </c>
       <c r="E299" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="H299" s="6"/>
       <c r="I299" s="6"/>
@@ -11275,10 +11257,10 @@
         <v>8.3000000000000001E-3</v>
       </c>
       <c r="E300" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="F300" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G300">
         <v>7</v>
@@ -11305,7 +11287,7 @@
         <v>8.3000000000000001E-3</v>
       </c>
       <c r="E301" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="H301" s="6"/>
       <c r="I301" s="6"/>
@@ -11329,10 +11311,10 @@
         <v>1.2178</v>
       </c>
       <c r="E302" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="F302" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G302">
         <v>7</v>
@@ -11359,7 +11341,7 @@
         <v>1.2178</v>
       </c>
       <c r="E303" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="H303" s="6"/>
       <c r="I303" s="6"/>
@@ -11383,7 +11365,7 @@
         <v>1.2178</v>
       </c>
       <c r="E304" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="H304" s="6"/>
       <c r="I304" s="6"/>
@@ -11407,10 +11389,10 @@
         <v>0.66249999999999998</v>
       </c>
       <c r="E305" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="F305" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G305">
         <v>7</v>
@@ -11437,10 +11419,10 @@
         <v>0.78900000000000003</v>
       </c>
       <c r="E306" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="F306" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G306">
         <v>7</v>
@@ -11467,7 +11449,7 @@
         <v>0.58630000000000004</v>
       </c>
       <c r="E307" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="H307" s="6"/>
       <c r="I307" s="6"/>
@@ -11491,7 +11473,7 @@
         <v>0.28739999999999999</v>
       </c>
       <c r="E308" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="H308" s="6"/>
       <c r="I308" s="6"/>
@@ -11515,10 +11497,10 @@
         <v>4.8300000000000003E-2</v>
       </c>
       <c r="E309" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="F309" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G309">
         <v>7</v>
@@ -11545,7 +11527,7 @@
         <v>4.1200000000000001E-2</v>
       </c>
       <c r="E310" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="H310" s="6"/>
       <c r="I310" s="6"/>
@@ -11569,7 +11551,7 @@
         <v>0.43380000000000002</v>
       </c>
       <c r="E311" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="H311" s="6"/>
       <c r="I311" s="6"/>
@@ -11593,7 +11575,7 @@
         <v>6.4000000000000003E-3</v>
       </c>
       <c r="E312" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="H312" s="6"/>
       <c r="I312" s="6"/>
@@ -11617,15 +11599,15 @@
         <v>0.87380000000000002</v>
       </c>
       <c r="E313" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="H313" s="6"/>
       <c r="I313" s="6"/>
       <c r="J313" s="6" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="K313" s="6" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
     </row>
     <row r="314" spans="1:13" x14ac:dyDescent="0.25">
@@ -11642,15 +11624,15 @@
         <v>0.18079999999999999</v>
       </c>
       <c r="E314" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="H314" s="6"/>
       <c r="I314" s="6"/>
       <c r="J314" s="6" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="K314" s="6" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
     </row>
     <row r="315" spans="1:13" x14ac:dyDescent="0.25">
@@ -11667,15 +11649,15 @@
         <v>1.7600000000000001E-2</v>
       </c>
       <c r="E315" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="H315" s="6"/>
       <c r="I315" s="6"/>
       <c r="J315" s="6" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="K315" s="6" t="s">
-        <v>994</v>
+        <v>988</v>
       </c>
     </row>
     <row r="316" spans="1:13" x14ac:dyDescent="0.25">
@@ -11692,15 +11674,15 @@
         <v>0.12909999999999999</v>
       </c>
       <c r="E316" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="H316" s="6"/>
       <c r="I316" s="6"/>
       <c r="J316" s="6" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="K316" t="s">
-        <v>995</v>
+        <v>989</v>
       </c>
     </row>
     <row r="317" spans="1:13" x14ac:dyDescent="0.25">
@@ -11717,15 +11699,15 @@
         <v>0.12909999999999999</v>
       </c>
       <c r="E317" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="H317" s="6"/>
       <c r="I317" s="6"/>
       <c r="J317" s="6" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="K317" s="6" t="s">
-        <v>996</v>
+        <v>990</v>
       </c>
     </row>
     <row r="318" spans="1:13" x14ac:dyDescent="0.25">
@@ -11742,15 +11724,15 @@
         <v>3.7199999999999997E-2</v>
       </c>
       <c r="E318" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="H318" s="6"/>
       <c r="I318" s="6"/>
       <c r="J318" s="6" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="K318" s="6" t="s">
-        <v>997</v>
+        <v>991</v>
       </c>
     </row>
     <row r="319" spans="1:13" x14ac:dyDescent="0.25">
@@ -11767,15 +11749,15 @@
         <v>0.1089</v>
       </c>
       <c r="E319" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="H319" s="6"/>
       <c r="I319" s="6"/>
       <c r="J319" s="6" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="K319" s="6" t="s">
-        <v>997</v>
+        <v>991</v>
       </c>
     </row>
     <row r="320" spans="1:13" x14ac:dyDescent="0.25">
@@ -11792,7 +11774,7 @@
         <v>1.1465000000000001</v>
       </c>
       <c r="E320" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="H320" s="6"/>
       <c r="I320" s="6"/>
@@ -11816,7 +11798,7 @@
         <v>0.33950000000000002</v>
       </c>
       <c r="E321" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="H321" s="6"/>
       <c r="I321" s="6"/>
@@ -11840,7 +11822,7 @@
         <v>4.7899999999999998E-2</v>
       </c>
       <c r="E322" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="H322" s="6"/>
       <c r="I322" s="6"/>
@@ -11864,7 +11846,7 @@
         <v>9.2999999999999999E-2</v>
       </c>
       <c r="E323" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="H323" s="6"/>
       <c r="I323" s="6"/>
@@ -11888,15 +11870,15 @@
         <v>3.85E-2</v>
       </c>
       <c r="E324" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="H324" s="6"/>
       <c r="I324" s="6"/>
       <c r="J324" s="6" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="K324" s="6" t="s">
-        <v>998</v>
+        <v>992</v>
       </c>
     </row>
     <row r="325" spans="1:13" x14ac:dyDescent="0.25">
@@ -11913,15 +11895,15 @@
         <v>9.8100000000000007E-2</v>
       </c>
       <c r="E325" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="H325" s="6"/>
       <c r="I325" s="6"/>
       <c r="J325" s="6" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="K325" s="6" t="s">
-        <v>999</v>
+        <v>993</v>
       </c>
     </row>
     <row r="326" spans="1:13" x14ac:dyDescent="0.25">
@@ -11938,15 +11920,15 @@
         <v>9.8100000000000007E-2</v>
       </c>
       <c r="E326" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="H326" s="6"/>
       <c r="I326" s="6"/>
       <c r="J326" s="6" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="K326" s="6" t="s">
-        <v>1000</v>
+        <v>994</v>
       </c>
     </row>
     <row r="327" spans="1:13" x14ac:dyDescent="0.25">
@@ -11963,15 +11945,15 @@
         <v>5.3199999999999997E-2</v>
       </c>
       <c r="E327" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="H327" s="6"/>
       <c r="I327" s="6"/>
       <c r="J327" s="6" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="K327" s="6" t="s">
-        <v>1001</v>
+        <v>995</v>
       </c>
     </row>
     <row r="328" spans="1:13" x14ac:dyDescent="0.25">
@@ -11988,15 +11970,15 @@
         <v>5.3199999999999997E-2</v>
       </c>
       <c r="E328" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="H328" s="6"/>
       <c r="I328" s="6"/>
       <c r="J328" s="6" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="K328" s="6" t="s">
-        <v>1002</v>
+        <v>996</v>
       </c>
     </row>
     <row r="329" spans="1:13" x14ac:dyDescent="0.25">
@@ -12013,15 +11995,15 @@
         <v>5.3199999999999997E-2</v>
       </c>
       <c r="E329" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="H329" s="6"/>
       <c r="I329" s="6"/>
       <c r="J329" s="6" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="K329" s="6" t="s">
-        <v>1003</v>
+        <v>997</v>
       </c>
     </row>
     <row r="330" spans="1:13" x14ac:dyDescent="0.25">
@@ -12038,15 +12020,15 @@
         <v>0.24229999999999999</v>
       </c>
       <c r="E330" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="H330" s="6"/>
       <c r="I330" s="6"/>
       <c r="J330" s="6" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="K330" s="6" t="s">
-        <v>1004</v>
+        <v>998</v>
       </c>
     </row>
     <row r="331" spans="1:13" x14ac:dyDescent="0.25">
@@ -12063,15 +12045,15 @@
         <v>0.24229999999999999</v>
       </c>
       <c r="E331" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="H331" s="6"/>
       <c r="I331" s="6"/>
       <c r="J331" s="6" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="K331" s="6" t="s">
-        <v>1005</v>
+        <v>999</v>
       </c>
     </row>
     <row r="332" spans="1:13" x14ac:dyDescent="0.25">
@@ -12088,7 +12070,7 @@
         <v>0.27839999999999998</v>
       </c>
       <c r="E332" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="H332" s="6"/>
       <c r="I332" s="6"/>
@@ -12112,7 +12094,7 @@
         <v>0.3765</v>
       </c>
       <c r="E333" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="H333" s="6"/>
       <c r="I333" s="6"/>
@@ -12136,7 +12118,7 @@
         <v>0.60170000000000001</v>
       </c>
       <c r="E334" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="H334" s="6"/>
       <c r="I334" s="6"/>
@@ -12160,7 +12142,7 @@
         <v>0.60170000000000001</v>
       </c>
       <c r="E335" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="H335" s="6"/>
       <c r="I335" s="6"/>
@@ -12184,7 +12166,7 @@
         <v>7.1499999999999994E-2</v>
       </c>
       <c r="E336" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="H336" s="6"/>
       <c r="I336" s="6"/>
@@ -12208,7 +12190,7 @@
         <v>9.2399999999999996E-2</v>
       </c>
       <c r="E337" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="H337" s="6"/>
       <c r="I337" s="6"/>
@@ -12232,7 +12214,7 @@
         <v>9.2399999999999996E-2</v>
       </c>
       <c r="E338" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="H338" s="6"/>
       <c r="I338" s="6"/>
@@ -12256,7 +12238,7 @@
         <v>0.2419</v>
       </c>
       <c r="E339" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="H339" s="6"/>
       <c r="I339" s="6"/>
@@ -12280,15 +12262,15 @@
         <v>0.12180000000000001</v>
       </c>
       <c r="E340" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="H340" s="6"/>
       <c r="I340" s="6"/>
       <c r="J340" s="6" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="K340" s="6" t="s">
-        <v>1006</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="341" spans="1:13" x14ac:dyDescent="0.25">
@@ -12305,15 +12287,15 @@
         <v>0.12180000000000001</v>
       </c>
       <c r="E341" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="H341" s="6"/>
       <c r="I341" s="6"/>
       <c r="J341" s="6" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="K341" s="6" t="s">
-        <v>1007</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="342" spans="1:13" x14ac:dyDescent="0.25">
@@ -12330,15 +12312,15 @@
         <v>4.82E-2</v>
       </c>
       <c r="E342" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="H342" s="6"/>
       <c r="I342" s="6"/>
       <c r="J342" s="6" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="K342" s="6" t="s">
-        <v>1008</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="343" spans="1:13" x14ac:dyDescent="0.25">
@@ -12355,15 +12337,15 @@
         <v>4.82E-2</v>
       </c>
       <c r="E343" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="H343" s="6"/>
       <c r="I343" s="6"/>
       <c r="J343" s="6" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="K343" s="6" t="s">
-        <v>1009</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="344" spans="1:13" x14ac:dyDescent="0.25">
@@ -12380,13 +12362,13 @@
         <v>3.4200000000000001E-2</v>
       </c>
       <c r="E344" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="H344" s="6" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="I344" s="6" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
       <c r="J344" s="6"/>
       <c r="K344" s="6"/>
@@ -12405,13 +12387,13 @@
         <v>3.4200000000000001E-2</v>
       </c>
       <c r="E345" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="H345" s="6" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="I345" s="6" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="J345" s="6"/>
       <c r="K345" s="6"/>
@@ -12430,13 +12412,13 @@
         <v>3.4200000000000001E-2</v>
       </c>
       <c r="E346" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="H346" s="6" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="I346" s="6" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
       <c r="J346" s="6"/>
       <c r="K346" s="6"/>
@@ -12455,13 +12437,13 @@
         <v>3.4200000000000001E-2</v>
       </c>
       <c r="E347" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="H347" s="6" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="I347" s="6" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="J347" s="6"/>
       <c r="K347" s="6"/>
@@ -12480,13 +12462,13 @@
         <v>3.4200000000000001E-2</v>
       </c>
       <c r="E348" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="H348" s="6" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="I348" s="6" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="J348" s="6"/>
       <c r="K348" s="6"/>
@@ -12505,7 +12487,7 @@
         <v>0.1182</v>
       </c>
       <c r="E349" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="H349" s="6"/>
       <c r="I349" s="6"/>
@@ -12529,7 +12511,7 @@
         <v>0.1182</v>
       </c>
       <c r="E350" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="H350" s="6"/>
       <c r="I350" s="6"/>
@@ -12553,7 +12535,7 @@
         <v>0.1182</v>
       </c>
       <c r="E351" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="H351" s="6"/>
       <c r="I351" s="6"/>
@@ -12577,7 +12559,7 @@
         <v>0.1182</v>
       </c>
       <c r="E352" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="H352" s="6"/>
       <c r="I352" s="6"/>
@@ -12601,7 +12583,7 @@
         <v>0.1182</v>
       </c>
       <c r="E353" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="H353" s="6"/>
       <c r="I353" s="6"/>
@@ -12625,7 +12607,7 @@
         <v>0.23980000000000001</v>
       </c>
       <c r="E354" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="H354" s="6"/>
       <c r="I354" s="6"/>
@@ -12649,7 +12631,7 @@
         <v>0.45860000000000001</v>
       </c>
       <c r="E355" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="H355" s="6"/>
       <c r="I355" s="6"/>
@@ -12661,25 +12643,19 @@
     </row>
     <row r="356" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A356">
-        <v>1020001</v>
+        <v>1020002</v>
       </c>
       <c r="B356" t="s">
         <v>363</v>
       </c>
       <c r="C356">
-        <v>0.79049999999999998</v>
+        <v>0</v>
       </c>
       <c r="D356">
         <v>0.27389999999999998</v>
       </c>
       <c r="E356" t="s">
-        <v>437</v>
-      </c>
-      <c r="F356" t="s">
-        <v>441</v>
-      </c>
-      <c r="G356">
-        <v>10</v>
+        <v>434</v>
       </c>
       <c r="H356" s="6"/>
       <c r="I356" s="6"/>
@@ -12691,61 +12667,61 @@
     </row>
     <row r="357" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A357">
-        <v>1020002</v>
+        <v>1040001</v>
       </c>
       <c r="B357" t="s">
         <v>364</v>
       </c>
       <c r="C357">
-        <v>0</v>
+        <v>0.81410000000000005</v>
       </c>
       <c r="D357">
-        <v>0.27389999999999998</v>
+        <v>0.3876</v>
       </c>
       <c r="E357" t="s">
-        <v>437</v>
+        <v>434</v>
+      </c>
+      <c r="F357" t="s">
+        <v>438</v>
+      </c>
+      <c r="G357">
+        <v>10</v>
       </c>
       <c r="H357" s="6"/>
       <c r="I357" s="6"/>
       <c r="J357" s="6"/>
       <c r="K357" s="6"/>
       <c r="M357">
-        <v>356000</v>
+        <v>660000</v>
       </c>
     </row>
     <row r="358" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A358">
-        <v>1040001</v>
+        <v>1040002</v>
       </c>
       <c r="B358" t="s">
         <v>365</v>
       </c>
       <c r="C358">
-        <v>0.81410000000000005</v>
+        <v>0</v>
       </c>
       <c r="D358">
         <v>0.3876</v>
       </c>
       <c r="E358" t="s">
-        <v>437</v>
-      </c>
-      <c r="F358" t="s">
-        <v>441</v>
-      </c>
-      <c r="G358">
-        <v>10</v>
+        <v>434</v>
       </c>
       <c r="H358" s="6"/>
       <c r="I358" s="6"/>
       <c r="J358" s="6"/>
       <c r="K358" s="6"/>
       <c r="M358">
-        <v>660</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="359" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A359">
-        <v>1040002</v>
+        <v>1111130</v>
       </c>
       <c r="B359" t="s">
         <v>366</v>
@@ -12754,22 +12730,22 @@
         <v>0</v>
       </c>
       <c r="D359">
-        <v>0.3876</v>
+        <v>0.68489999999999995</v>
       </c>
       <c r="E359" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="H359" s="6"/>
       <c r="I359" s="6"/>
       <c r="J359" s="6"/>
       <c r="K359" s="6"/>
       <c r="M359">
-        <v>4800</v>
+        <v>150</v>
       </c>
     </row>
     <row r="360" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A360">
-        <v>1111130</v>
+        <v>1111131</v>
       </c>
       <c r="B360" t="s">
         <v>367</v>
@@ -12781,19 +12757,19 @@
         <v>0.68489999999999995</v>
       </c>
       <c r="E360" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="H360" s="6"/>
       <c r="I360" s="6"/>
       <c r="J360" s="6"/>
       <c r="K360" s="6"/>
       <c r="M360">
-        <v>150</v>
+        <v>240</v>
       </c>
     </row>
     <row r="361" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A361">
-        <v>1111131</v>
+        <v>1111132</v>
       </c>
       <c r="B361" t="s">
         <v>368</v>
@@ -12805,19 +12781,19 @@
         <v>0.68489999999999995</v>
       </c>
       <c r="E361" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="H361" s="6"/>
       <c r="I361" s="6"/>
       <c r="J361" s="6"/>
       <c r="K361" s="6"/>
       <c r="M361">
-        <v>240</v>
+        <v>495</v>
       </c>
     </row>
     <row r="362" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A362">
-        <v>1111132</v>
+        <v>1111133</v>
       </c>
       <c r="B362" t="s">
         <v>369</v>
@@ -12829,19 +12805,19 @@
         <v>0.68489999999999995</v>
       </c>
       <c r="E362" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="H362" s="6"/>
       <c r="I362" s="6"/>
       <c r="J362" s="6"/>
       <c r="K362" s="6"/>
       <c r="M362">
-        <v>495</v>
+        <v>370</v>
       </c>
     </row>
     <row r="363" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A363">
-        <v>1111133</v>
+        <v>1111135</v>
       </c>
       <c r="B363" t="s">
         <v>370</v>
@@ -12853,19 +12829,19 @@
         <v>0.68489999999999995</v>
       </c>
       <c r="E363" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="H363" s="6"/>
       <c r="I363" s="6"/>
       <c r="J363" s="6"/>
       <c r="K363" s="6"/>
       <c r="M363">
-        <v>370</v>
+        <v>170</v>
       </c>
     </row>
     <row r="364" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A364">
-        <v>1111135</v>
+        <v>1111144</v>
       </c>
       <c r="B364" t="s">
         <v>371</v>
@@ -12877,19 +12853,19 @@
         <v>0.68489999999999995</v>
       </c>
       <c r="E364" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="H364" s="6"/>
       <c r="I364" s="6"/>
       <c r="J364" s="6"/>
       <c r="K364" s="6"/>
       <c r="M364">
-        <v>170</v>
+        <v>450</v>
       </c>
     </row>
     <row r="365" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A365">
-        <v>1111144</v>
+        <v>1111148</v>
       </c>
       <c r="B365" t="s">
         <v>372</v>
@@ -12901,19 +12877,19 @@
         <v>0.68489999999999995</v>
       </c>
       <c r="E365" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="H365" s="6"/>
       <c r="I365" s="6"/>
       <c r="J365" s="6"/>
       <c r="K365" s="6"/>
       <c r="M365">
-        <v>450</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="366" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A366">
-        <v>1111148</v>
+        <v>1111152</v>
       </c>
       <c r="B366" t="s">
         <v>373</v>
@@ -12925,19 +12901,19 @@
         <v>0.68489999999999995</v>
       </c>
       <c r="E366" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="H366" s="6"/>
       <c r="I366" s="6"/>
       <c r="J366" s="6"/>
       <c r="K366" s="6"/>
       <c r="M366">
-        <v>1250</v>
+        <v>210</v>
       </c>
     </row>
     <row r="367" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A367">
-        <v>1111152</v>
+        <v>1111153</v>
       </c>
       <c r="B367" t="s">
         <v>374</v>
@@ -12949,22 +12925,22 @@
         <v>0.68489999999999995</v>
       </c>
       <c r="E367" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="H367" s="6"/>
       <c r="I367" s="6"/>
       <c r="J367" s="6"/>
       <c r="K367" s="6"/>
       <c r="M367">
-        <v>210</v>
+        <v>100</v>
       </c>
     </row>
     <row r="368" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A368">
-        <v>1111153</v>
+        <v>1111155</v>
       </c>
       <c r="B368" t="s">
-        <v>375</v>
+        <v>40</v>
       </c>
       <c r="C368">
         <v>0</v>
@@ -12973,22 +12949,22 @@
         <v>0.68489999999999995</v>
       </c>
       <c r="E368" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="H368" s="6"/>
       <c r="I368" s="6"/>
       <c r="J368" s="6"/>
       <c r="K368" s="6"/>
       <c r="M368">
-        <v>100</v>
+        <v>70</v>
       </c>
     </row>
     <row r="369" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A369">
-        <v>1111155</v>
+        <v>1111156</v>
       </c>
       <c r="B369" t="s">
-        <v>40</v>
+        <v>375</v>
       </c>
       <c r="C369">
         <v>0</v>
@@ -12997,19 +12973,19 @@
         <v>0.68489999999999995</v>
       </c>
       <c r="E369" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="H369" s="6"/>
       <c r="I369" s="6"/>
       <c r="J369" s="6"/>
       <c r="K369" s="6"/>
       <c r="M369">
-        <v>70</v>
+        <v>650</v>
       </c>
     </row>
     <row r="370" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A370">
-        <v>1111156</v>
+        <v>1111207</v>
       </c>
       <c r="B370" t="s">
         <v>376</v>
@@ -13018,22 +12994,22 @@
         <v>0</v>
       </c>
       <c r="D370">
-        <v>0.68489999999999995</v>
+        <v>0.1255</v>
       </c>
       <c r="E370" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="H370" s="6"/>
       <c r="I370" s="6"/>
       <c r="J370" s="6"/>
       <c r="K370" s="6"/>
       <c r="M370">
-        <v>650</v>
+        <v>430</v>
       </c>
     </row>
     <row r="371" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A371">
-        <v>1111207</v>
+        <v>1111231</v>
       </c>
       <c r="B371" t="s">
         <v>377</v>
@@ -13045,19 +13021,19 @@
         <v>0.1255</v>
       </c>
       <c r="E371" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="H371" s="6"/>
       <c r="I371" s="6"/>
       <c r="J371" s="6"/>
       <c r="K371" s="6"/>
       <c r="M371">
-        <v>430</v>
+        <v>370</v>
       </c>
     </row>
     <row r="372" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A372">
-        <v>1111231</v>
+        <v>1111237</v>
       </c>
       <c r="B372" t="s">
         <v>378</v>
@@ -13069,19 +13045,19 @@
         <v>0.1255</v>
       </c>
       <c r="E372" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="H372" s="6"/>
       <c r="I372" s="6"/>
       <c r="J372" s="6"/>
       <c r="K372" s="6"/>
       <c r="M372">
-        <v>370</v>
+        <v>360</v>
       </c>
     </row>
     <row r="373" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A373">
-        <v>1111237</v>
+        <v>1112108</v>
       </c>
       <c r="B373" t="s">
         <v>379</v>
@@ -13090,22 +13066,22 @@
         <v>0</v>
       </c>
       <c r="D373">
-        <v>0.1255</v>
+        <v>0.17560000000000001</v>
       </c>
       <c r="E373" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="H373" s="6"/>
       <c r="I373" s="6"/>
       <c r="J373" s="6"/>
       <c r="K373" s="6"/>
       <c r="M373">
-        <v>360</v>
+        <v>85</v>
       </c>
     </row>
     <row r="374" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A374">
-        <v>1112108</v>
+        <v>1112113</v>
       </c>
       <c r="B374" t="s">
         <v>380</v>
@@ -13117,19 +13093,19 @@
         <v>0.17560000000000001</v>
       </c>
       <c r="E374" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="H374" s="6"/>
       <c r="I374" s="6"/>
       <c r="J374" s="6"/>
       <c r="K374" s="6"/>
       <c r="M374">
-        <v>85</v>
+        <v>20</v>
       </c>
     </row>
     <row r="375" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A375">
-        <v>1112113</v>
+        <v>1112120</v>
       </c>
       <c r="B375" t="s">
         <v>381</v>
@@ -13141,7 +13117,7 @@
         <v>0.17560000000000001</v>
       </c>
       <c r="E375" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="H375" s="6"/>
       <c r="I375" s="6"/>
@@ -13153,61 +13129,61 @@
     </row>
     <row r="376" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A376">
-        <v>1112120</v>
+        <v>1120101</v>
       </c>
       <c r="B376" t="s">
         <v>382</v>
       </c>
       <c r="C376">
-        <v>0</v>
+        <v>0.49990000000000001</v>
       </c>
       <c r="D376">
-        <v>0.17560000000000001</v>
+        <v>2.5895999999999999</v>
       </c>
       <c r="E376" t="s">
+        <v>435</v>
+      </c>
+      <c r="F376" t="s">
         <v>438</v>
+      </c>
+      <c r="G376">
+        <v>11</v>
       </c>
       <c r="H376" s="6"/>
       <c r="I376" s="6"/>
       <c r="J376" s="6"/>
       <c r="K376" s="6"/>
       <c r="M376">
-        <v>20</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="377" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A377">
-        <v>1120101</v>
+        <v>1120301</v>
       </c>
       <c r="B377" t="s">
         <v>383</v>
       </c>
       <c r="C377">
-        <v>0.49990000000000001</v>
+        <v>0</v>
       </c>
       <c r="D377">
-        <v>2.5895999999999999</v>
+        <v>5.3900000000000003E-2</v>
       </c>
       <c r="E377" t="s">
-        <v>438</v>
-      </c>
-      <c r="F377" t="s">
-        <v>441</v>
-      </c>
-      <c r="G377">
-        <v>11</v>
+        <v>435</v>
       </c>
       <c r="H377" s="6"/>
       <c r="I377" s="6"/>
       <c r="J377" s="6"/>
       <c r="K377" s="6"/>
       <c r="M377">
-        <v>3500</v>
+        <v>3380</v>
       </c>
     </row>
     <row r="378" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A378">
-        <v>1120301</v>
+        <v>1120398</v>
       </c>
       <c r="B378" t="s">
         <v>384</v>
@@ -13219,19 +13195,19 @@
         <v>5.3900000000000003E-2</v>
       </c>
       <c r="E378" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="H378" s="6"/>
       <c r="I378" s="6"/>
       <c r="J378" s="6"/>
       <c r="K378" s="6"/>
       <c r="M378">
-        <v>3380</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="379" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A379">
-        <v>1120398</v>
+        <v>1212098</v>
       </c>
       <c r="B379" t="s">
         <v>385</v>
@@ -13240,22 +13216,22 @@
         <v>0</v>
       </c>
       <c r="D379">
-        <v>5.3900000000000003E-2</v>
+        <v>2.8199999999999999E-2</v>
       </c>
       <c r="E379" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="H379" s="6"/>
       <c r="I379" s="6"/>
       <c r="J379" s="6"/>
       <c r="K379" s="6"/>
       <c r="M379">
-        <v>1250</v>
+        <v>23522</v>
       </c>
     </row>
     <row r="380" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A380">
-        <v>1212098</v>
+        <v>1214101</v>
       </c>
       <c r="B380" t="s">
         <v>386</v>
@@ -13264,84 +13240,70 @@
         <v>0</v>
       </c>
       <c r="D380">
-        <v>2.8199999999999999E-2</v>
+        <v>0.35420000000000001</v>
       </c>
       <c r="E380" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="H380" s="6"/>
       <c r="I380" s="6"/>
       <c r="J380" s="6"/>
       <c r="K380" s="6"/>
       <c r="M380">
-        <v>23522</v>
+        <v>44733</v>
       </c>
     </row>
     <row r="381" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A381">
-        <v>1213001</v>
+        <v>1222001</v>
       </c>
       <c r="B381" t="s">
         <v>387</v>
       </c>
       <c r="C381">
-        <v>0.95609999999999995</v>
+        <v>0</v>
       </c>
       <c r="D381">
-        <v>2.29E-2</v>
+        <v>0.2417</v>
       </c>
       <c r="E381" t="s">
-        <v>439</v>
-      </c>
-      <c r="F381" t="s">
-        <v>441</v>
-      </c>
-      <c r="G381">
-        <v>12</v>
-      </c>
-      <c r="H381" s="6" t="s">
-        <v>698</v>
-      </c>
-      <c r="I381" s="6" t="s">
-        <v>867</v>
-      </c>
+        <v>436</v>
+      </c>
+      <c r="H381" s="6"/>
+      <c r="I381" s="6"/>
       <c r="J381" s="6"/>
       <c r="K381" s="6"/>
+      <c r="M381">
+        <v>40</v>
+      </c>
     </row>
     <row r="382" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A382">
-        <v>1213002</v>
+        <v>1222002</v>
       </c>
       <c r="B382" t="s">
         <v>388</v>
       </c>
       <c r="C382">
-        <v>0.95609999999999995</v>
+        <v>0</v>
       </c>
       <c r="D382">
-        <v>2.29E-2</v>
+        <v>0.2417</v>
       </c>
       <c r="E382" t="s">
-        <v>439</v>
-      </c>
-      <c r="F382" t="s">
-        <v>441</v>
-      </c>
-      <c r="G382">
-        <v>12</v>
-      </c>
-      <c r="H382" s="6" t="s">
-        <v>699</v>
-      </c>
-      <c r="I382" s="6" t="s">
-        <v>868</v>
-      </c>
+        <v>436</v>
+      </c>
+      <c r="H382" s="6"/>
+      <c r="I382" s="6"/>
       <c r="J382" s="6"/>
       <c r="K382" s="6"/>
+      <c r="M382">
+        <v>1107</v>
+      </c>
     </row>
     <row r="383" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A383">
-        <v>1214101</v>
+        <v>1229101</v>
       </c>
       <c r="B383" t="s">
         <v>389</v>
@@ -13350,22 +13312,22 @@
         <v>0</v>
       </c>
       <c r="D383">
-        <v>0.35420000000000001</v>
+        <v>0.16239999999999999</v>
       </c>
       <c r="E383" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="H383" s="6"/>
       <c r="I383" s="6"/>
       <c r="J383" s="6"/>
       <c r="K383" s="6"/>
       <c r="M383">
-        <v>44733</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="384" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A384">
-        <v>1222001</v>
+        <v>1311101</v>
       </c>
       <c r="B384" t="s">
         <v>390</v>
@@ -13374,22 +13336,23 @@
         <v>0</v>
       </c>
       <c r="D384">
-        <v>0.2417</v>
+        <v>2.1299999999999999E-2</v>
       </c>
       <c r="E384" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="H384" s="6"/>
       <c r="I384" s="6"/>
-      <c r="J384" s="6"/>
-      <c r="K384" s="6"/>
-      <c r="M384">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="385" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J384" s="6" t="s">
+        <v>698</v>
+      </c>
+      <c r="K384" s="6" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="385" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A385">
-        <v>1222002</v>
+        <v>1311103</v>
       </c>
       <c r="B385" t="s">
         <v>391</v>
@@ -13398,22 +13361,23 @@
         <v>0</v>
       </c>
       <c r="D385">
-        <v>0.2417</v>
+        <v>2.1299999999999999E-2</v>
       </c>
       <c r="E385" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="H385" s="6"/>
       <c r="I385" s="6"/>
-      <c r="J385" s="6"/>
-      <c r="K385" s="6"/>
-      <c r="M385">
-        <v>1107</v>
-      </c>
-    </row>
-    <row r="386" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J385" s="6" t="s">
+        <v>699</v>
+      </c>
+      <c r="K385" s="6" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="386" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A386">
-        <v>1229101</v>
+        <v>1311104</v>
       </c>
       <c r="B386" t="s">
         <v>392</v>
@@ -13422,22 +13386,23 @@
         <v>0</v>
       </c>
       <c r="D386">
-        <v>0.16239999999999999</v>
+        <v>2.1299999999999999E-2</v>
       </c>
       <c r="E386" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="H386" s="6"/>
       <c r="I386" s="6"/>
-      <c r="J386" s="6"/>
-      <c r="K386" s="6"/>
-      <c r="M386">
-        <v>16.8</v>
-      </c>
-    </row>
-    <row r="387" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J386" s="6" t="s">
+        <v>700</v>
+      </c>
+      <c r="K386" s="6" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="387" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A387">
-        <v>1311101</v>
+        <v>1312001</v>
       </c>
       <c r="B387" t="s">
         <v>393</v>
@@ -13446,23 +13411,23 @@
         <v>0</v>
       </c>
       <c r="D387">
-        <v>2.1299999999999999E-2</v>
+        <v>8.1500000000000003E-2</v>
       </c>
       <c r="E387" t="s">
-        <v>440</v>
-      </c>
-      <c r="H387" s="6"/>
-      <c r="I387" s="6"/>
-      <c r="J387" s="6" t="s">
-        <v>702</v>
-      </c>
-      <c r="K387" s="6" t="s">
-        <v>1010</v>
-      </c>
-    </row>
-    <row r="388" spans="1:13" x14ac:dyDescent="0.25">
+        <v>437</v>
+      </c>
+      <c r="H387" s="6" t="s">
+        <v>701</v>
+      </c>
+      <c r="I387" s="6" t="s">
+        <v>863</v>
+      </c>
+      <c r="J387" s="6"/>
+      <c r="K387" s="6"/>
+    </row>
+    <row r="388" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A388">
-        <v>1311103</v>
+        <v>1312002</v>
       </c>
       <c r="B388" t="s">
         <v>394</v>
@@ -13471,23 +13436,23 @@
         <v>0</v>
       </c>
       <c r="D388">
-        <v>2.1299999999999999E-2</v>
+        <v>8.1500000000000003E-2</v>
       </c>
       <c r="E388" t="s">
-        <v>440</v>
-      </c>
-      <c r="H388" s="6"/>
-      <c r="I388" s="6"/>
-      <c r="J388" s="6" t="s">
-        <v>703</v>
-      </c>
-      <c r="K388" s="6" t="s">
-        <v>1011</v>
-      </c>
-    </row>
-    <row r="389" spans="1:13" x14ac:dyDescent="0.25">
+        <v>437</v>
+      </c>
+      <c r="H388" s="6" t="s">
+        <v>702</v>
+      </c>
+      <c r="I388" s="6" t="s">
+        <v>864</v>
+      </c>
+      <c r="J388" s="6"/>
+      <c r="K388" s="6"/>
+    </row>
+    <row r="389" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A389">
-        <v>1311104</v>
+        <v>1312016</v>
       </c>
       <c r="B389" t="s">
         <v>395</v>
@@ -13496,23 +13461,23 @@
         <v>0</v>
       </c>
       <c r="D389">
-        <v>2.1299999999999999E-2</v>
+        <v>8.1500000000000003E-2</v>
       </c>
       <c r="E389" t="s">
-        <v>440</v>
-      </c>
-      <c r="H389" s="6"/>
-      <c r="I389" s="6"/>
-      <c r="J389" s="6" t="s">
-        <v>704</v>
-      </c>
-      <c r="K389" s="6" t="s">
-        <v>1012</v>
-      </c>
-    </row>
-    <row r="390" spans="1:13" x14ac:dyDescent="0.25">
+        <v>437</v>
+      </c>
+      <c r="H389" s="6" t="s">
+        <v>695</v>
+      </c>
+      <c r="I389" s="6" t="s">
+        <v>863</v>
+      </c>
+      <c r="J389" s="6"/>
+      <c r="K389" s="6"/>
+    </row>
+    <row r="390" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A390">
-        <v>1312001</v>
+        <v>1312017</v>
       </c>
       <c r="B390" t="s">
         <v>396</v>
@@ -13524,20 +13489,20 @@
         <v>8.1500000000000003E-2</v>
       </c>
       <c r="E390" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="H390" s="6" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="I390" s="6" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
       <c r="J390" s="6"/>
       <c r="K390" s="6"/>
     </row>
-    <row r="391" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A391">
-        <v>1312002</v>
+        <v>1312018</v>
       </c>
       <c r="B391" t="s">
         <v>397</v>
@@ -13549,20 +13514,20 @@
         <v>8.1500000000000003E-2</v>
       </c>
       <c r="E391" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="H391" s="6" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="I391" s="6" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
       <c r="J391" s="6"/>
       <c r="K391" s="6"/>
     </row>
-    <row r="392" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A392">
-        <v>1312016</v>
+        <v>1312019</v>
       </c>
       <c r="B392" t="s">
         <v>398</v>
@@ -13574,20 +13539,20 @@
         <v>8.1500000000000003E-2</v>
       </c>
       <c r="E392" t="s">
-        <v>440</v>
-      </c>
-      <c r="H392" s="6" t="s">
-        <v>698</v>
-      </c>
-      <c r="I392" s="6" t="s">
-        <v>869</v>
-      </c>
-      <c r="J392" s="6"/>
-      <c r="K392" s="6"/>
-    </row>
-    <row r="393" spans="1:13" x14ac:dyDescent="0.25">
+        <v>437</v>
+      </c>
+      <c r="H392" s="6"/>
+      <c r="I392" s="6"/>
+      <c r="J392" s="6" t="s">
+        <v>705</v>
+      </c>
+      <c r="K392" s="6" t="s">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="393" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A393">
-        <v>1312017</v>
+        <v>1312020</v>
       </c>
       <c r="B393" t="s">
         <v>399</v>
@@ -13599,20 +13564,20 @@
         <v>8.1500000000000003E-2</v>
       </c>
       <c r="E393" t="s">
-        <v>440</v>
-      </c>
-      <c r="H393" s="6" t="s">
-        <v>707</v>
-      </c>
-      <c r="I393" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="J393" s="6"/>
-      <c r="K393" s="6"/>
-    </row>
-    <row r="394" spans="1:13" x14ac:dyDescent="0.25">
+        <v>437</v>
+      </c>
+      <c r="H393" s="6"/>
+      <c r="I393" s="6"/>
+      <c r="J393" s="6" t="s">
+        <v>706</v>
+      </c>
+      <c r="K393" s="6" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="394" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A394">
-        <v>1312018</v>
+        <v>1312021</v>
       </c>
       <c r="B394" t="s">
         <v>400</v>
@@ -13624,20 +13589,20 @@
         <v>8.1500000000000003E-2</v>
       </c>
       <c r="E394" t="s">
-        <v>440</v>
-      </c>
-      <c r="H394" s="6" t="s">
-        <v>708</v>
-      </c>
-      <c r="I394" s="6" t="s">
-        <v>872</v>
-      </c>
-      <c r="J394" s="6"/>
-      <c r="K394" s="6"/>
-    </row>
-    <row r="395" spans="1:13" x14ac:dyDescent="0.25">
+        <v>437</v>
+      </c>
+      <c r="H394" s="6"/>
+      <c r="I394" s="6"/>
+      <c r="J394" s="6" t="s">
+        <v>707</v>
+      </c>
+      <c r="K394" s="6" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="395" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A395">
-        <v>1312019</v>
+        <v>1312022</v>
       </c>
       <c r="B395" t="s">
         <v>401</v>
@@ -13649,20 +13614,20 @@
         <v>8.1500000000000003E-2</v>
       </c>
       <c r="E395" t="s">
-        <v>440</v>
-      </c>
-      <c r="H395" s="6"/>
-      <c r="I395" s="6"/>
-      <c r="J395" s="6" t="s">
-        <v>709</v>
-      </c>
-      <c r="K395" s="6" t="s">
-        <v>1013</v>
-      </c>
-    </row>
-    <row r="396" spans="1:13" x14ac:dyDescent="0.25">
+        <v>437</v>
+      </c>
+      <c r="H395" s="6" t="s">
+        <v>708</v>
+      </c>
+      <c r="I395" s="6" t="s">
+        <v>867</v>
+      </c>
+      <c r="J395" s="6"/>
+      <c r="K395" s="6"/>
+    </row>
+    <row r="396" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A396">
-        <v>1312020</v>
+        <v>1312023</v>
       </c>
       <c r="B396" t="s">
         <v>402</v>
@@ -13674,20 +13639,20 @@
         <v>8.1500000000000003E-2</v>
       </c>
       <c r="E396" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="H396" s="6"/>
       <c r="I396" s="6"/>
       <c r="J396" s="6" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="K396" s="6" t="s">
-        <v>1014</v>
-      </c>
-    </row>
-    <row r="397" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="397" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A397">
-        <v>1312021</v>
+        <v>1312024</v>
       </c>
       <c r="B397" t="s">
         <v>403</v>
@@ -13699,20 +13664,20 @@
         <v>8.1500000000000003E-2</v>
       </c>
       <c r="E397" t="s">
-        <v>440</v>
-      </c>
-      <c r="H397" s="6"/>
-      <c r="I397" s="6"/>
-      <c r="J397" s="6" t="s">
-        <v>711</v>
-      </c>
-      <c r="K397" s="6" t="s">
-        <v>1015</v>
-      </c>
-    </row>
-    <row r="398" spans="1:13" x14ac:dyDescent="0.25">
+        <v>437</v>
+      </c>
+      <c r="H397" s="6" t="s">
+        <v>710</v>
+      </c>
+      <c r="I397" s="6" t="s">
+        <v>868</v>
+      </c>
+      <c r="J397" s="6"/>
+      <c r="K397" s="6"/>
+    </row>
+    <row r="398" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A398">
-        <v>1312022</v>
+        <v>1312025</v>
       </c>
       <c r="B398" t="s">
         <v>404</v>
@@ -13724,20 +13689,20 @@
         <v>8.1500000000000003E-2</v>
       </c>
       <c r="E398" t="s">
-        <v>440</v>
-      </c>
-      <c r="H398" s="6" t="s">
-        <v>712</v>
-      </c>
-      <c r="I398" s="6" t="s">
-        <v>873</v>
-      </c>
-      <c r="J398" s="6"/>
-      <c r="K398" s="6"/>
-    </row>
-    <row r="399" spans="1:13" x14ac:dyDescent="0.25">
+        <v>437</v>
+      </c>
+      <c r="H398" s="6"/>
+      <c r="I398" s="6"/>
+      <c r="J398" s="6" t="s">
+        <v>711</v>
+      </c>
+      <c r="K398" s="6" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="399" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A399">
-        <v>1312023</v>
+        <v>1312026</v>
       </c>
       <c r="B399" t="s">
         <v>405</v>
@@ -13749,20 +13714,20 @@
         <v>8.1500000000000003E-2</v>
       </c>
       <c r="E399" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="H399" s="6"/>
       <c r="I399" s="6"/>
       <c r="J399" s="6" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="K399" s="6" t="s">
-        <v>1016</v>
-      </c>
-    </row>
-    <row r="400" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="400" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A400">
-        <v>1312024</v>
+        <v>1312027</v>
       </c>
       <c r="B400" t="s">
         <v>406</v>
@@ -13774,20 +13739,20 @@
         <v>8.1500000000000003E-2</v>
       </c>
       <c r="E400" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="H400" s="6" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="I400" s="6" t="s">
-        <v>874</v>
+        <v>869</v>
       </c>
       <c r="J400" s="6"/>
       <c r="K400" s="6"/>
     </row>
     <row r="401" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A401">
-        <v>1312025</v>
+        <v>1312030</v>
       </c>
       <c r="B401" t="s">
         <v>407</v>
@@ -13799,20 +13764,20 @@
         <v>8.1500000000000003E-2</v>
       </c>
       <c r="E401" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="H401" s="6"/>
       <c r="I401" s="6"/>
       <c r="J401" s="6" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="K401" s="6" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="402" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A402">
-        <v>1312026</v>
+        <v>1313101</v>
       </c>
       <c r="B402" t="s">
         <v>408</v>
@@ -13821,23 +13786,22 @@
         <v>0</v>
       </c>
       <c r="D402">
-        <v>8.1500000000000003E-2</v>
+        <v>0.19639999999999999</v>
       </c>
       <c r="E402" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="H402" s="6"/>
       <c r="I402" s="6"/>
-      <c r="J402" s="6" t="s">
-        <v>716</v>
-      </c>
-      <c r="K402" s="6" t="s">
-        <v>1018</v>
+      <c r="J402" s="6"/>
+      <c r="K402" s="6"/>
+      <c r="M402">
+        <v>500</v>
       </c>
     </row>
     <row r="403" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A403">
-        <v>1312027</v>
+        <v>1313102</v>
       </c>
       <c r="B403" t="s">
         <v>409</v>
@@ -13846,23 +13810,22 @@
         <v>0</v>
       </c>
       <c r="D403">
-        <v>8.1500000000000003E-2</v>
+        <v>0.19639999999999999</v>
       </c>
       <c r="E403" t="s">
-        <v>440</v>
-      </c>
-      <c r="H403" s="6" t="s">
-        <v>717</v>
-      </c>
-      <c r="I403" s="6" t="s">
-        <v>875</v>
-      </c>
+        <v>437</v>
+      </c>
+      <c r="H403" s="6"/>
+      <c r="I403" s="6"/>
       <c r="J403" s="6"/>
       <c r="K403" s="6"/>
+      <c r="M403">
+        <v>1100</v>
+      </c>
     </row>
     <row r="404" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A404">
-        <v>1312030</v>
+        <v>1313202</v>
       </c>
       <c r="B404" t="s">
         <v>410</v>
@@ -13871,23 +13834,22 @@
         <v>0</v>
       </c>
       <c r="D404">
-        <v>8.1500000000000003E-2</v>
+        <v>0.1925</v>
       </c>
       <c r="E404" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="H404" s="6"/>
       <c r="I404" s="6"/>
-      <c r="J404" s="6" t="s">
-        <v>718</v>
-      </c>
-      <c r="K404" s="6" t="s">
-        <v>1019</v>
+      <c r="J404" s="6"/>
+      <c r="K404" s="6"/>
+      <c r="M404">
+        <v>500</v>
       </c>
     </row>
     <row r="405" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A405">
-        <v>1313101</v>
+        <v>1321101</v>
       </c>
       <c r="B405" t="s">
         <v>411</v>
@@ -13896,22 +13858,23 @@
         <v>0</v>
       </c>
       <c r="D405">
-        <v>0.19639999999999999</v>
+        <v>0.22450000000000001</v>
       </c>
       <c r="E405" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="H405" s="6"/>
       <c r="I405" s="6"/>
-      <c r="J405" s="6"/>
-      <c r="K405" s="6"/>
-      <c r="M405">
-        <v>500</v>
+      <c r="J405" s="6" t="s">
+        <v>715</v>
+      </c>
+      <c r="K405" s="6" t="s">
+        <v>1014</v>
       </c>
     </row>
     <row r="406" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A406">
-        <v>1313102</v>
+        <v>1321105</v>
       </c>
       <c r="B406" t="s">
         <v>412</v>
@@ -13920,22 +13883,23 @@
         <v>0</v>
       </c>
       <c r="D406">
-        <v>0.19639999999999999</v>
+        <v>0.22450000000000001</v>
       </c>
       <c r="E406" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="H406" s="6"/>
       <c r="I406" s="6"/>
-      <c r="J406" s="6"/>
-      <c r="K406" s="6"/>
-      <c r="M406">
-        <v>1100</v>
+      <c r="J406" s="6" t="s">
+        <v>696</v>
+      </c>
+      <c r="K406" s="6" t="s">
+        <v>1015</v>
       </c>
     </row>
     <row r="407" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A407">
-        <v>1313202</v>
+        <v>1329101</v>
       </c>
       <c r="B407" t="s">
         <v>413</v>
@@ -13944,22 +13908,23 @@
         <v>0</v>
       </c>
       <c r="D407">
-        <v>0.1925</v>
+        <v>0.1075</v>
       </c>
       <c r="E407" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="H407" s="6"/>
       <c r="I407" s="6"/>
-      <c r="J407" s="6"/>
-      <c r="K407" s="6"/>
-      <c r="M407">
-        <v>500</v>
+      <c r="J407" s="6" t="s">
+        <v>697</v>
+      </c>
+      <c r="K407" s="6" t="s">
+        <v>1016</v>
       </c>
     </row>
     <row r="408" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A408">
-        <v>1321101</v>
+        <v>1329104</v>
       </c>
       <c r="B408" t="s">
         <v>414</v>
@@ -13968,23 +13933,23 @@
         <v>0</v>
       </c>
       <c r="D408">
-        <v>0.22450000000000001</v>
+        <v>0.1075</v>
       </c>
       <c r="E408" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="H408" s="6"/>
       <c r="I408" s="6"/>
       <c r="J408" s="6" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="K408" s="6" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="409" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A409">
-        <v>1321105</v>
+        <v>1329106</v>
       </c>
       <c r="B409" t="s">
         <v>415</v>
@@ -13993,23 +13958,23 @@
         <v>0</v>
       </c>
       <c r="D409">
-        <v>0.22450000000000001</v>
+        <v>0.1075</v>
       </c>
       <c r="E409" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="H409" s="6"/>
       <c r="I409" s="6"/>
       <c r="J409" s="6" t="s">
-        <v>700</v>
+        <v>717</v>
       </c>
       <c r="K409" s="6" t="s">
-        <v>1021</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="410" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A410">
-        <v>1329101</v>
+        <v>1329111</v>
       </c>
       <c r="B410" t="s">
         <v>416</v>
@@ -14021,20 +13986,20 @@
         <v>0.1075</v>
       </c>
       <c r="E410" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="H410" s="6"/>
       <c r="I410" s="6"/>
       <c r="J410" s="6" t="s">
-        <v>701</v>
+        <v>448</v>
       </c>
       <c r="K410" s="6" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="411" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A411">
-        <v>1329104</v>
+        <v>1329114</v>
       </c>
       <c r="B411" t="s">
         <v>417</v>
@@ -14046,20 +14011,20 @@
         <v>0.1075</v>
       </c>
       <c r="E411" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="H411" s="6"/>
       <c r="I411" s="6"/>
       <c r="J411" s="6" t="s">
-        <v>720</v>
+        <v>447</v>
       </c>
       <c r="K411" s="6" t="s">
-        <v>1023</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="412" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A412">
-        <v>1329106</v>
+        <v>1329129</v>
       </c>
       <c r="B412" t="s">
         <v>418</v>
@@ -14071,20 +14036,20 @@
         <v>0.1075</v>
       </c>
       <c r="E412" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="H412" s="6"/>
       <c r="I412" s="6"/>
       <c r="J412" s="6" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="K412" s="6" t="s">
-        <v>1024</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="413" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A413">
-        <v>1329111</v>
+        <v>1330101</v>
       </c>
       <c r="B413" t="s">
         <v>419</v>
@@ -14093,23 +14058,23 @@
         <v>0</v>
       </c>
       <c r="D413">
-        <v>0.1075</v>
+        <v>0.35170000000000001</v>
       </c>
       <c r="E413" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="H413" s="6"/>
       <c r="I413" s="6"/>
-      <c r="J413" s="6" t="s">
-        <v>451</v>
-      </c>
-      <c r="K413" s="6" t="s">
-        <v>1025</v>
+      <c r="J413" s="6"/>
+      <c r="K413" s="6"/>
+      <c r="L413" s="6"/>
+      <c r="M413">
+        <v>5000</v>
       </c>
     </row>
     <row r="414" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A414">
-        <v>1329114</v>
+        <v>1390208</v>
       </c>
       <c r="B414" t="s">
         <v>420</v>
@@ -14118,23 +14083,23 @@
         <v>0</v>
       </c>
       <c r="D414">
-        <v>0.1075</v>
+        <v>0.4022</v>
       </c>
       <c r="E414" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="H414" s="6"/>
       <c r="I414" s="6"/>
-      <c r="J414" s="6" t="s">
-        <v>450</v>
-      </c>
-      <c r="K414" s="6" t="s">
-        <v>1026</v>
+      <c r="J414" s="6"/>
+      <c r="K414" s="6"/>
+      <c r="L414" s="6"/>
+      <c r="M414">
+        <v>271459</v>
       </c>
     </row>
     <row r="415" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A415">
-        <v>1329129</v>
+        <v>1390901</v>
       </c>
       <c r="B415" t="s">
         <v>421</v>
@@ -14143,23 +14108,23 @@
         <v>0</v>
       </c>
       <c r="D415">
-        <v>0.1075</v>
+        <v>0.19339999999999999</v>
       </c>
       <c r="E415" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="H415" s="6"/>
       <c r="I415" s="6"/>
-      <c r="J415" s="6" t="s">
-        <v>722</v>
-      </c>
-      <c r="K415" s="6" t="s">
-        <v>1027</v>
+      <c r="J415" s="6"/>
+      <c r="K415" s="6"/>
+      <c r="L415" s="6"/>
+      <c r="M415">
+        <v>44.56</v>
       </c>
     </row>
     <row r="416" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A416">
-        <v>1330101</v>
+        <v>1390902</v>
       </c>
       <c r="B416" t="s">
         <v>422</v>
@@ -14168,10 +14133,10 @@
         <v>0</v>
       </c>
       <c r="D416">
-        <v>0.35170000000000001</v>
+        <v>0.19339999999999999</v>
       </c>
       <c r="E416" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="H416" s="6"/>
       <c r="I416" s="6"/>
@@ -14179,12 +14144,12 @@
       <c r="K416" s="6"/>
       <c r="L416" s="6"/>
       <c r="M416">
-        <v>5000</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="417" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A417">
-        <v>1390208</v>
+        <v>1390903</v>
       </c>
       <c r="B417" t="s">
         <v>423</v>
@@ -14193,10 +14158,10 @@
         <v>0</v>
       </c>
       <c r="D417">
-        <v>0.4022</v>
+        <v>0.19339999999999999</v>
       </c>
       <c r="E417" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="H417" s="6"/>
       <c r="I417" s="6"/>
@@ -14204,12 +14169,12 @@
       <c r="K417" s="6"/>
       <c r="L417" s="6"/>
       <c r="M417">
-        <v>271459</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="418" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A418">
-        <v>1390901</v>
+        <v>1390906</v>
       </c>
       <c r="B418" t="s">
         <v>424</v>
@@ -14221,7 +14186,7 @@
         <v>0.19339999999999999</v>
       </c>
       <c r="E418" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="H418" s="6"/>
       <c r="I418" s="6"/>
@@ -14229,83 +14194,29 @@
       <c r="K418" s="6"/>
       <c r="L418" s="6"/>
       <c r="M418">
-        <v>44.56</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="419" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A419">
-        <v>1390902</v>
-      </c>
-      <c r="B419" t="s">
-        <v>425</v>
-      </c>
-      <c r="C419">
-        <v>0</v>
-      </c>
-      <c r="D419">
-        <v>0.19339999999999999</v>
-      </c>
-      <c r="E419" t="s">
-        <v>440</v>
-      </c>
-      <c r="H419" s="6"/>
-      <c r="I419" s="6"/>
-      <c r="J419" s="6"/>
-      <c r="K419" s="6"/>
-      <c r="L419" s="6"/>
-      <c r="M419">
-        <v>5200</v>
-      </c>
+      <c r="H419" s="3"/>
+      <c r="I419" s="3"/>
+      <c r="J419" s="3"/>
+      <c r="K419" s="3"/>
+      <c r="L419" s="3"/>
     </row>
     <row r="420" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A420">
-        <v>1390903</v>
-      </c>
-      <c r="B420" t="s">
-        <v>426</v>
-      </c>
-      <c r="C420">
-        <v>0</v>
-      </c>
-      <c r="D420">
-        <v>0.19339999999999999</v>
-      </c>
-      <c r="E420" t="s">
-        <v>440</v>
-      </c>
-      <c r="H420" s="6"/>
-      <c r="I420" s="6"/>
-      <c r="J420" s="6"/>
-      <c r="K420" s="6"/>
-      <c r="L420" s="6"/>
-      <c r="M420">
-        <v>2500</v>
-      </c>
+      <c r="H420" s="3"/>
+      <c r="I420" s="3"/>
+      <c r="J420" s="3"/>
+      <c r="K420" s="3"/>
+      <c r="L420" s="3"/>
     </row>
     <row r="421" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A421">
-        <v>1390906</v>
-      </c>
-      <c r="B421" t="s">
-        <v>427</v>
-      </c>
-      <c r="C421">
-        <v>0</v>
-      </c>
-      <c r="D421">
-        <v>0.19339999999999999</v>
-      </c>
-      <c r="E421" t="s">
-        <v>440</v>
-      </c>
-      <c r="H421" s="6"/>
-      <c r="I421" s="6"/>
-      <c r="J421" s="6"/>
-      <c r="K421" s="6"/>
-      <c r="L421" s="6"/>
-      <c r="M421">
-        <v>2000</v>
-      </c>
+      <c r="H421" s="3"/>
+      <c r="I421" s="3"/>
+      <c r="J421" s="3"/>
+      <c r="K421" s="3"/>
+      <c r="L421" s="3"/>
     </row>
     <row r="422" spans="1:13" x14ac:dyDescent="0.25">
       <c r="H422" s="3"/>
@@ -14511,11 +14422,11 @@
       <c r="L450" s="3"/>
     </row>
     <row r="451" spans="8:12" x14ac:dyDescent="0.25">
-      <c r="H451" s="3"/>
-      <c r="I451" s="3"/>
-      <c r="J451" s="3"/>
-      <c r="K451" s="3"/>
-      <c r="L451" s="3"/>
+      <c r="H451" s="4"/>
+      <c r="I451" s="4"/>
+      <c r="J451" s="4"/>
+      <c r="K451" s="4"/>
+      <c r="L451" s="4"/>
     </row>
     <row r="452" spans="8:12" x14ac:dyDescent="0.25">
       <c r="H452" s="3"/>
@@ -14532,11 +14443,11 @@
       <c r="L453" s="3"/>
     </row>
     <row r="454" spans="8:12" x14ac:dyDescent="0.25">
-      <c r="H454" s="4"/>
-      <c r="I454" s="4"/>
-      <c r="J454" s="4"/>
-      <c r="K454" s="4"/>
-      <c r="L454" s="4"/>
+      <c r="H454" s="3"/>
+      <c r="I454" s="3"/>
+      <c r="J454" s="3"/>
+      <c r="K454" s="3"/>
+      <c r="L454" s="3"/>
     </row>
     <row r="455" spans="8:12" x14ac:dyDescent="0.25">
       <c r="H455" s="3"/>
@@ -15386,11 +15297,11 @@
       <c r="L575" s="3"/>
     </row>
     <row r="576" spans="8:12" x14ac:dyDescent="0.25">
-      <c r="H576" s="3"/>
-      <c r="I576" s="3"/>
-      <c r="J576" s="3"/>
-      <c r="K576" s="3"/>
-      <c r="L576" s="3"/>
+      <c r="H576" s="4"/>
+      <c r="I576" s="4"/>
+      <c r="J576" s="4"/>
+      <c r="K576" s="4"/>
+      <c r="L576" s="4"/>
     </row>
     <row r="577" spans="8:12" x14ac:dyDescent="0.25">
       <c r="H577" s="3"/>
@@ -15407,34 +15318,14 @@
       <c r="L578" s="3"/>
     </row>
     <row r="579" spans="8:12" x14ac:dyDescent="0.25">
-      <c r="H579" s="4"/>
-      <c r="I579" s="4"/>
-      <c r="J579" s="4"/>
-      <c r="K579" s="4"/>
-      <c r="L579" s="4"/>
-    </row>
-    <row r="580" spans="8:12" x14ac:dyDescent="0.25">
-      <c r="H580" s="3"/>
-      <c r="I580" s="3"/>
-      <c r="J580" s="3"/>
-      <c r="K580" s="3"/>
-      <c r="L580" s="3"/>
-    </row>
-    <row r="581" spans="8:12" x14ac:dyDescent="0.25">
-      <c r="H581" s="3"/>
-      <c r="I581" s="3"/>
-      <c r="J581" s="3"/>
-      <c r="K581" s="3"/>
-      <c r="L581" s="3"/>
-    </row>
-    <row r="582" spans="8:12" x14ac:dyDescent="0.25">
-      <c r="H582" s="2"/>
-      <c r="I582" s="2"/>
-      <c r="J582" s="2"/>
-      <c r="K582" s="2"/>
-      <c r="L582" s="2"/>
+      <c r="H579" s="2"/>
+      <c r="I579" s="2"/>
+      <c r="J579" s="2"/>
+      <c r="K579" s="2"/>
+      <c r="L579" s="2"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:M418" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <hyperlinks>
     <hyperlink ref="H63" r:id="rId1" xr:uid="{1A708F42-224F-491F-9EC0-62C518D7C16A}"/>
     <hyperlink ref="H75" r:id="rId2" xr:uid="{99E2ECD4-14B3-4FB5-B56A-F2D82C630699}"/>
@@ -15466,7 +15357,7 @@
     <hyperlink ref="K216" r:id="rId28" xr:uid="{7873197F-A36E-47EC-90B3-7125D39FE48E}"/>
     <hyperlink ref="K218" r:id="rId29" xr:uid="{F315F7A3-90A1-4027-8725-BC5ED8A6AC9C}"/>
     <hyperlink ref="J315" r:id="rId30" xr:uid="{A27211FE-D1E5-4CEF-950D-A55437A518EB}"/>
-    <hyperlink ref="J404" r:id="rId31" xr:uid="{9DEE7333-C438-4E9D-AE4A-6784E2852E68}"/>
+    <hyperlink ref="J401" r:id="rId31" xr:uid="{9DEE7333-C438-4E9D-AE4A-6784E2852E68}"/>
     <hyperlink ref="J183" r:id="rId32" xr:uid="{85A50750-79E7-4B9D-BF10-4B547FDD4FCE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15487,7 +15378,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC963DF5-A225-429F-BD5C-188557DDB4F0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93E58AD7-6155-4C5B-9A68-9476491E1F82}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>

--- a/TUFE_Konfigurasyon.xlsx
+++ b/TUFE_Konfigurasyon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\vb41981\Desktop\Fiyat_Veritabani\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF596620-7426-4345-93FE-A7D6EB6F416B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A6C67F0-2D05-4019-BDAA-F6D91E7C51F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1465" uniqueCount="1022">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1465" uniqueCount="1023">
   <si>
     <t>Kod</t>
   </si>
@@ -3103,6 +3103,9 @@
   </si>
   <si>
     <t>https://www.hepsiburada.com/prima-bebek-bezi-premium-care-5-numara-74-adet-ultra-firsat-paketi-p-HBV00000GD85U</t>
+  </si>
+  <si>
+    <t>Ayran (Servis edilen)</t>
   </si>
 </sst>
 </file>
@@ -3544,17 +3547,18 @@
   <dimension ref="A1:O579"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="51.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="16.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="27.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="115.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="111.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="184.5703125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="255.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="13.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -12940,7 +12944,7 @@
         <v>1111155</v>
       </c>
       <c r="B368" t="s">
-        <v>40</v>
+        <v>1022</v>
       </c>
       <c r="C368">
         <v>0</v>
@@ -15378,7 +15382,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93E58AD7-6155-4C5B-9A68-9476491E1F82}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0794BAD7-DD24-47E3-A002-5F9C9C737FE0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>

--- a/TUFE_Konfigurasyon.xlsx
+++ b/TUFE_Konfigurasyon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\vb41981\Desktop\Fiyat_Veritabani\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A6C67F0-2D05-4019-BDAA-F6D91E7C51F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ED4F9D4-480A-4912-B348-FC26B32DE14C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3184,7 +3184,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -3202,6 +3202,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Köprü" xfId="1" builtinId="8"/>
@@ -3551,18 +3552,18 @@
     <col min="2" max="2" width="51.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="16.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="27.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="115.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="111.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="184.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="255.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.7109375" customWidth="1"/>
+    <col min="7" max="7" width="20.140625" customWidth="1"/>
+    <col min="8" max="8" width="115.85546875" customWidth="1"/>
+    <col min="9" max="9" width="111.140625" customWidth="1"/>
+    <col min="10" max="10" width="184.5703125" customWidth="1"/>
+    <col min="11" max="11" width="255.7109375" customWidth="1"/>
+    <col min="12" max="12" width="17" customWidth="1"/>
     <col min="13" max="13" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="13.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -12743,8 +12744,8 @@
       <c r="I359" s="6"/>
       <c r="J359" s="6"/>
       <c r="K359" s="6"/>
-      <c r="M359">
-        <v>150</v>
+      <c r="M359" s="7">
+        <v>140</v>
       </c>
     </row>
     <row r="360" spans="1:13" x14ac:dyDescent="0.25">
@@ -12767,8 +12768,8 @@
       <c r="I360" s="6"/>
       <c r="J360" s="6"/>
       <c r="K360" s="6"/>
-      <c r="M360">
-        <v>240</v>
+      <c r="M360" s="7">
+        <v>270</v>
       </c>
     </row>
     <row r="361" spans="1:13" x14ac:dyDescent="0.25">
@@ -12791,8 +12792,8 @@
       <c r="I361" s="6"/>
       <c r="J361" s="6"/>
       <c r="K361" s="6"/>
-      <c r="M361">
-        <v>495</v>
+      <c r="M361" s="7">
+        <v>490</v>
       </c>
     </row>
     <row r="362" spans="1:13" x14ac:dyDescent="0.25">
@@ -12815,7 +12816,7 @@
       <c r="I362" s="6"/>
       <c r="J362" s="6"/>
       <c r="K362" s="6"/>
-      <c r="M362">
+      <c r="M362" s="7">
         <v>370</v>
       </c>
     </row>
@@ -12839,7 +12840,7 @@
       <c r="I363" s="6"/>
       <c r="J363" s="6"/>
       <c r="K363" s="6"/>
-      <c r="M363">
+      <c r="M363" s="7">
         <v>170</v>
       </c>
     </row>
@@ -15382,7 +15383,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0794BAD7-DD24-47E3-A002-5F9C9C737FE0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D5C1F0C-E738-4F30-84C3-C3FD52D04024}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>

--- a/TUFE_Konfigurasyon.xlsx
+++ b/TUFE_Konfigurasyon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\vb41981\Desktop\Fiyat_Veritabani\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ED4F9D4-480A-4912-B348-FC26B32DE14C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0962F801-0AB0-49F8-822F-BF3065404B5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13159,7 +13159,7 @@
       <c r="J376" s="6"/>
       <c r="K376" s="6"/>
       <c r="M376">
-        <v>3500</v>
+        <v>2575</v>
       </c>
     </row>
     <row r="377" spans="1:13" x14ac:dyDescent="0.25">
@@ -15383,7 +15383,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D5C1F0C-E738-4F30-84C3-C3FD52D04024}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D45F50F1-37B5-43C1-BF6F-5935B42A08EA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>

--- a/TUFE_Konfigurasyon.xlsx
+++ b/TUFE_Konfigurasyon.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\vb41981\Desktop\Fiyat_Veritabani\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0962F801-0AB0-49F8-822F-BF3065404B5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A887A68E-3730-4694-B362-EC1CB104959D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20052" yWindow="-420" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Madde_Sepeti" sheetId="1" r:id="rId1"/>
@@ -3550,15 +3550,15 @@
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="51.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="27.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.7109375" customWidth="1"/>
-    <col min="7" max="7" width="20.140625" customWidth="1"/>
-    <col min="8" max="8" width="115.85546875" customWidth="1"/>
-    <col min="9" max="9" width="111.140625" customWidth="1"/>
-    <col min="10" max="10" width="184.5703125" customWidth="1"/>
-    <col min="11" max="11" width="255.7109375" customWidth="1"/>
-    <col min="12" max="12" width="17" customWidth="1"/>
+    <col min="3" max="4" width="16.28515625" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="27.140625" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="19.7109375" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="20.140625" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="115.85546875" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="111.140625" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="184.5703125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="255.7109375" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="17" hidden="1" customWidth="1"/>
     <col min="13" max="13" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="13.28515625" bestFit="1" customWidth="1"/>
   </cols>
@@ -6798,7 +6798,7 @@
       <c r="K124" s="6"/>
       <c r="L124" s="6"/>
       <c r="M124">
-        <v>1475</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.25">
@@ -6823,7 +6823,7 @@
       <c r="K125" s="6"/>
       <c r="L125" s="6"/>
       <c r="M125">
-        <v>575</v>
+        <v>715</v>
       </c>
     </row>
     <row r="126" spans="1:13" x14ac:dyDescent="0.25">
@@ -6848,7 +6848,7 @@
       <c r="K126" s="6"/>
       <c r="L126" s="6"/>
       <c r="M126">
-        <v>775</v>
+        <v>750</v>
       </c>
     </row>
     <row r="127" spans="1:13" x14ac:dyDescent="0.25">
@@ -6873,7 +6873,7 @@
       <c r="K127" s="6"/>
       <c r="L127" s="6"/>
       <c r="M127">
-        <v>1080</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="128" spans="1:13" x14ac:dyDescent="0.25">
@@ -6898,7 +6898,7 @@
       <c r="K128" s="6"/>
       <c r="L128" s="6"/>
       <c r="M128">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="129" spans="1:13" x14ac:dyDescent="0.25">
@@ -10340,7 +10340,7 @@
       <c r="J263" s="6"/>
       <c r="K263" s="6"/>
       <c r="M263">
-        <v>1850</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="264" spans="1:13" x14ac:dyDescent="0.25">
@@ -10490,7 +10490,7 @@
       <c r="J269" s="6"/>
       <c r="K269" s="6"/>
       <c r="M269">
-        <v>2500</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="270" spans="1:13" x14ac:dyDescent="0.25">
@@ -10658,7 +10658,7 @@
       <c r="J276" s="6"/>
       <c r="K276" s="6"/>
       <c r="M276">
-        <v>2400</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="277" spans="1:13" x14ac:dyDescent="0.25">
@@ -12721,7 +12721,7 @@
       <c r="J358" s="6"/>
       <c r="K358" s="6"/>
       <c r="M358">
-        <v>4800</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="359" spans="1:13" x14ac:dyDescent="0.25">
@@ -15383,7 +15383,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D45F50F1-37B5-43C1-BF6F-5935B42A08EA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B5EFED3-25B1-42BB-B456-8FC23DE23F9D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>

--- a/TUFE_Konfigurasyon.xlsx
+++ b/TUFE_Konfigurasyon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\vb41981\Desktop\Fiyat_Veritabani\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A887A68E-3730-4694-B362-EC1CB104959D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2FD1783-D664-46F4-913B-C8ACF1456754}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20052" yWindow="-420" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6848,7 +6848,7 @@
       <c r="K126" s="6"/>
       <c r="L126" s="6"/>
       <c r="M126">
-        <v>750</v>
+        <v>800</v>
       </c>
     </row>
     <row r="127" spans="1:13" x14ac:dyDescent="0.25">
@@ -6873,7 +6873,7 @@
       <c r="K127" s="6"/>
       <c r="L127" s="6"/>
       <c r="M127">
-        <v>1000</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="128" spans="1:13" x14ac:dyDescent="0.25">
@@ -6898,7 +6898,7 @@
       <c r="K128" s="6"/>
       <c r="L128" s="6"/>
       <c r="M128">
-        <v>85</v>
+        <v>108</v>
       </c>
     </row>
     <row r="129" spans="1:13" x14ac:dyDescent="0.25">
@@ -15383,7 +15383,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B5EFED3-25B1-42BB-B456-8FC23DE23F9D}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E9373985-AD3D-4C8F-B765-F4310156A6EE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>

--- a/TUFE_Konfigurasyon.xlsx
+++ b/TUFE_Konfigurasyon.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\vb41981\Desktop\Fiyat_Veritabani\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2FD1783-D664-46F4-913B-C8ACF1456754}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26B766F2-957D-4DF2-A31D-B17D63F5F4AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20052" yWindow="-420" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Madde_Sepeti" sheetId="1" r:id="rId1"/>
@@ -3550,15 +3550,15 @@
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="51.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="16.28515625" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="27.140625" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="19.7109375" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="20.140625" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="115.85546875" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="111.140625" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="184.5703125" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="255.7109375" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="17" hidden="1" customWidth="1"/>
+    <col min="3" max="4" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="115.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="111.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="184.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="255.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="13.28515625" bestFit="1" customWidth="1"/>
   </cols>
@@ -10920,7 +10920,7 @@
       <c r="J286" s="6"/>
       <c r="K286" s="6"/>
       <c r="M286">
-        <v>60.39</v>
+        <v>63.53</v>
       </c>
     </row>
     <row r="287" spans="1:13" x14ac:dyDescent="0.25">
@@ -10944,7 +10944,7 @@
       <c r="J287" s="6"/>
       <c r="K287" s="6"/>
       <c r="M287">
-        <v>58.34</v>
+        <v>59.34</v>
       </c>
     </row>
     <row r="288" spans="1:13" x14ac:dyDescent="0.25">
@@ -15383,7 +15383,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E9373985-AD3D-4C8F-B765-F4310156A6EE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D145520-76BE-43E5-8F3E-3F20AC926E6A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
